--- a/DataAnalysis/LT/0.05/Results.xlsx
+++ b/DataAnalysis/LT/0.05/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LT\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F659BE1-D73C-469A-BE5D-52727838C23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E907A2-3BD4-4730-AFC9-5EC06CA68C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="77">
   <si>
     <t>Dati originali</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>EER0_STD</t>
+  </si>
+  <si>
+    <t>try3</t>
   </si>
 </sst>
 </file>
@@ -597,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -843,369 +846,404 @@
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11">
+        <v>27</v>
+      </c>
+      <c r="H11">
+        <v>2.6770630673681683</v>
+      </c>
+      <c r="I11">
+        <v>24.25</v>
+      </c>
+      <c r="J11">
+        <v>1.1902380714238083</v>
+      </c>
+      <c r="K11">
+        <v>8.625</v>
+      </c>
+      <c r="L11">
+        <v>1.7888543819998326</v>
+      </c>
+      <c r="M11">
+        <v>19.958333333333332</v>
+      </c>
+      <c r="N11">
+        <v>0.55067298893330685</v>
+      </c>
+      <c r="O11">
+        <v>11.333333333333332</v>
+      </c>
+      <c r="P11">
+        <v>1.9340994650588066</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12">
-        <v>31.8</v>
-      </c>
-      <c r="H12">
-        <v>3.4496376621320741</v>
-      </c>
-      <c r="I12">
-        <v>30.25</v>
-      </c>
-      <c r="J12">
-        <v>3.2850672240711707</v>
-      </c>
-      <c r="K12">
-        <v>12.25</v>
-      </c>
-      <c r="L12">
-        <v>1.7677669529663689</v>
-      </c>
-      <c r="M12">
-        <v>24.766666666666666</v>
-      </c>
-      <c r="N12">
-        <v>1.4890547171334187</v>
-      </c>
-      <c r="O12">
-        <v>12.516666666666666</v>
-      </c>
-      <c r="P12">
-        <v>1.8026900338174325</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>31.8</v>
+      </c>
+      <c r="H13">
+        <v>3.4496376621320741</v>
+      </c>
+      <c r="I13">
+        <v>30.25</v>
+      </c>
+      <c r="J13">
+        <v>3.2850672240711707</v>
+      </c>
+      <c r="K13">
+        <v>12.25</v>
+      </c>
+      <c r="L13">
+        <v>1.7677669529663689</v>
+      </c>
+      <c r="M13">
+        <v>24.766666666666666</v>
+      </c>
+      <c r="N13">
+        <v>1.4890547171334187</v>
+      </c>
+      <c r="O13">
+        <v>12.516666666666666</v>
+      </c>
+      <c r="P13">
+        <v>1.8026900338174325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
         <v>2</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>21</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>29.5625</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>4.8361547594284922</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>26</v>
       </c>
-      <c r="J13">
+      <c r="J14">
         <v>4.5747755604588329</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>11.1875</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>2.2509918448795601</v>
       </c>
-      <c r="M13">
+      <c r="M14">
         <v>22.25</v>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>2.8702082220799161</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>11.062499999999998</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>3.1896876246518548</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16">
-        <v>36.642857142857146</v>
-      </c>
-      <c r="H16">
-        <v>4.9135381491199581</v>
-      </c>
-      <c r="I16">
-        <v>32.5</v>
-      </c>
-      <c r="J16">
-        <v>4.9413223601245315</v>
-      </c>
-      <c r="K16">
-        <v>11</v>
-      </c>
-      <c r="L16">
-        <v>1.9148542155126762</v>
-      </c>
-      <c r="M16">
-        <v>26.714285714285712</v>
-      </c>
-      <c r="N16">
-        <v>3.0470299529856346</v>
-      </c>
-      <c r="O16">
-        <v>15.714285714285714</v>
-      </c>
-      <c r="P16">
-        <v>3.5207247329921398</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G17">
-        <v>27.25</v>
+        <v>36.642857142857146</v>
       </c>
       <c r="H17">
-        <v>4.6124830622995248</v>
+        <v>4.9135381491199581</v>
       </c>
       <c r="I17">
-        <v>27.833333333333332</v>
+        <v>32.5</v>
       </c>
       <c r="J17">
-        <v>2.9944392908634274</v>
+        <v>4.9413223601245315</v>
       </c>
       <c r="K17">
-        <v>10.416666666666666</v>
+        <v>11</v>
       </c>
       <c r="L17">
-        <v>2.8533605917701106</v>
+        <v>1.9148542155126762</v>
       </c>
       <c r="M17">
-        <v>21.833333333333332</v>
+        <v>26.714285714285712</v>
       </c>
       <c r="N17">
-        <v>2.3452078799117149</v>
+        <v>3.0470299529856346</v>
       </c>
       <c r="O17">
-        <v>11.416666666666664</v>
+        <v>15.714285714285714</v>
       </c>
       <c r="P17">
-        <v>3.2158461820595017</v>
+        <v>3.5207247329921398</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18">
+        <v>27.25</v>
+      </c>
+      <c r="H18">
+        <v>4.6124830622995248</v>
+      </c>
+      <c r="I18">
+        <v>27.833333333333332</v>
+      </c>
+      <c r="J18">
+        <v>2.9944392908634274</v>
+      </c>
+      <c r="K18">
+        <v>10.416666666666666</v>
+      </c>
+      <c r="L18">
+        <v>2.8533605917701106</v>
+      </c>
+      <c r="M18">
+        <v>21.833333333333332</v>
+      </c>
+      <c r="N18">
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="O18">
+        <v>11.416666666666664</v>
+      </c>
+      <c r="P18">
+        <v>3.2158461820595017</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19">
-        <v>25.666666666666668</v>
-      </c>
-      <c r="H19">
-        <v>2.9297326385411577</v>
-      </c>
-      <c r="I19">
-        <v>27.333333333333332</v>
-      </c>
-      <c r="J19">
-        <v>5.3463383107818059</v>
-      </c>
-      <c r="K19">
-        <v>10.666666666666666</v>
-      </c>
-      <c r="L19">
-        <v>0.57735026918962573</v>
-      </c>
-      <c r="M19">
-        <v>21.222222222222218</v>
-      </c>
-      <c r="N19">
-        <v>1.1706281947614148</v>
-      </c>
-      <c r="O19">
-        <v>10.555555555555555</v>
-      </c>
-      <c r="P19">
-        <v>1.677740985615729</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>25.666666666666668</v>
+      </c>
+      <c r="H20">
+        <v>2.9297326385411577</v>
+      </c>
+      <c r="I20">
+        <v>27.333333333333332</v>
+      </c>
+      <c r="J20">
+        <v>5.3463383107818059</v>
+      </c>
+      <c r="K20">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="L20">
+        <v>0.57735026918962573</v>
+      </c>
+      <c r="M20">
+        <v>21.222222222222218</v>
+      </c>
+      <c r="N20">
+        <v>1.1706281947614148</v>
+      </c>
+      <c r="O20">
+        <v>10.555555555555555</v>
+      </c>
+      <c r="P20">
+        <v>1.677740985615729</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E21" t="s">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E22" t="s">
         <v>68</v>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>31.875</v>
       </c>
-      <c r="H21">
+      <c r="H22">
         <v>2.2867371223353739</v>
       </c>
-      <c r="I21">
+      <c r="I22">
         <v>27.5</v>
       </c>
-      <c r="J21">
+      <c r="J22">
         <v>3.5590260840104371</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>8.125</v>
       </c>
-      <c r="L21">
+      <c r="L22">
         <v>2.056493779875511</v>
       </c>
-      <c r="M21">
+      <c r="M22">
         <v>22.5</v>
       </c>
-      <c r="N21">
+      <c r="N22">
         <v>1.3402597868683137</v>
       </c>
-      <c r="O21">
+      <c r="O22">
         <v>14.375</v>
       </c>
-      <c r="P21">
+      <c r="P22">
         <v>2.532657073480697</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
-        <v>4</v>
-      </c>
-      <c r="G24">
-        <v>23.833333333333332</v>
-      </c>
-      <c r="H24">
-        <v>3.6968455021364766</v>
-      </c>
-      <c r="I24">
-        <v>22</v>
-      </c>
-      <c r="J24">
-        <v>3.03315017762062</v>
-      </c>
-      <c r="K24">
-        <v>8.5833333333333339</v>
-      </c>
-      <c r="L24">
-        <v>1.9853631070075477</v>
-      </c>
-      <c r="M24">
-        <v>18.138888888888889</v>
-      </c>
-      <c r="N24">
-        <v>2.2959303770576787</v>
-      </c>
-      <c r="O24">
-        <v>9.5555555555555554</v>
-      </c>
-      <c r="P24">
-        <v>1.9254629073050034</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="G25">
-        <v>18.666666666666668</v>
+        <v>23.833333333333332</v>
       </c>
       <c r="H25">
-        <v>5.9651767227244301</v>
+        <v>3.6968455021364766</v>
       </c>
       <c r="I25">
-        <v>19.333333333333332</v>
+        <v>22</v>
       </c>
       <c r="J25">
-        <v>3.6855573979160021</v>
+        <v>3.03315017762062</v>
       </c>
       <c r="K25">
-        <v>10.5</v>
+        <v>8.5833333333333339</v>
       </c>
       <c r="L25">
-        <v>0.5</v>
+        <v>1.9853631070075477</v>
       </c>
       <c r="M25">
-        <v>16.166666666666668</v>
+        <v>18.138888888888889</v>
       </c>
       <c r="N25">
-        <v>3.3706247360261101</v>
+        <v>2.2959303770576787</v>
       </c>
       <c r="O25">
-        <v>5.666666666666667</v>
+        <v>9.5555555555555554</v>
       </c>
       <c r="P25">
-        <v>2.9059326290271166</v>
+        <v>1.9254629073050034</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="H26">
+        <v>5.9651767227244301</v>
+      </c>
+      <c r="I26">
+        <v>19.333333333333332</v>
+      </c>
+      <c r="J26">
+        <v>3.6855573979160021</v>
+      </c>
+      <c r="K26">
+        <v>10.5</v>
+      </c>
+      <c r="L26">
+        <v>0.5</v>
+      </c>
+      <c r="M26">
+        <v>16.166666666666668</v>
+      </c>
+      <c r="N26">
+        <v>3.3706247360261101</v>
+      </c>
+      <c r="O26">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="P26">
+        <v>2.9059326290271166</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D27" t="s">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E28" t="s">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E29" t="s">
         <v>68</v>
       </c>
-      <c r="G28">
+      <c r="G29">
         <v>21.5</v>
       </c>
-      <c r="H28">
+      <c r="H29">
         <v>4.5</v>
       </c>
-      <c r="I28">
+      <c r="I29">
         <v>22.666666666666668</v>
       </c>
-      <c r="J28">
+      <c r="J29">
         <v>3.8188130791298716</v>
       </c>
-      <c r="K28">
+      <c r="K29">
         <v>10.666666666666666</v>
       </c>
-      <c r="L28">
+      <c r="L29">
         <v>0.28867513459481292</v>
       </c>
-      <c r="M28">
+      <c r="M29">
         <v>18.277777777777775</v>
       </c>
-      <c r="N28">
+      <c r="N29">
         <v>2.3589859717291444</v>
       </c>
-      <c r="O28">
+      <c r="O29">
         <v>7.6111111111111107</v>
       </c>
-      <c r="P28">
+      <c r="P29">
         <v>2.0705161281760218</v>
       </c>
     </row>
@@ -5200,7 +5238,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -5553,6 +5591,361 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>10.666666666666668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>72</v>
+      </c>
+      <c r="C9">
+        <v>28</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>85</v>
+      </c>
+      <c r="H9">
+        <v>15</v>
+      </c>
+      <c r="I9">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>68</v>
+      </c>
+      <c r="L9">
+        <v>86</v>
+      </c>
+      <c r="M9">
+        <v>14</v>
+      </c>
+      <c r="N9">
+        <v>7</v>
+      </c>
+      <c r="O9">
+        <v>93</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C9,D9)</f>
+        <v>24</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R8:R13" si="7">AVERAGE(H9,I9)</f>
+        <v>23.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S8:S13" si="8">AVERAGE(M9,N9)</f>
+        <v>10.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q9:S9)</f>
+        <v>19.333333333333332</v>
+      </c>
+      <c r="U9">
+        <f>AVERAGE(Q9:Q12)</f>
+        <v>27</v>
+      </c>
+      <c r="V9">
+        <f>_xlfn.STDEV.S(Q9:Q12)</f>
+        <v>2.6770630673681683</v>
+      </c>
+      <c r="W9">
+        <f>AVERAGE(R9:R12)</f>
+        <v>24.25</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.STDEV.S(R9:R12)</f>
+        <v>1.1902380714238083</v>
+      </c>
+      <c r="Y9">
+        <f>AVERAGE(S9:S12)</f>
+        <v>8.625</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.STDEV.S(S9:S13)</f>
+        <v>1.7888543819998326</v>
+      </c>
+      <c r="AA9">
+        <f>AVERAGE(T9:T12)</f>
+        <v>19.958333333333332</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.STDEV.S(T9:T12)</f>
+        <v>0.55067298893330685</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC8:AC13" si="10">MIN(Q9:S9)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD8:AD13" si="11">(T9-AC9)</f>
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="AE9">
+        <f>AVERAGE(AD9:AD12)</f>
+        <v>11.333333333333332</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.STDEV.S(AD9:AD12)</f>
+        <v>1.9340994650588066</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>70</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>23</v>
+      </c>
+      <c r="E10">
+        <v>77</v>
+      </c>
+      <c r="G10">
+        <v>72</v>
+      </c>
+      <c r="H10">
+        <v>28</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
+      </c>
+      <c r="J10">
+        <v>76</v>
+      </c>
+      <c r="L10">
+        <v>93</v>
+      </c>
+      <c r="M10">
+        <v>7</v>
+      </c>
+      <c r="N10">
+        <v>8</v>
+      </c>
+      <c r="O10">
+        <v>92</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>26.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="8"/>
+        <v>7.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="10"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="11"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>73</v>
+      </c>
+      <c r="C11">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>66</v>
+      </c>
+      <c r="G11">
+        <v>89</v>
+      </c>
+      <c r="H11">
+        <v>11</v>
+      </c>
+      <c r="I11">
+        <v>37</v>
+      </c>
+      <c r="J11">
+        <v>63</v>
+      </c>
+      <c r="L11">
+        <v>93</v>
+      </c>
+      <c r="M11">
+        <v>7</v>
+      </c>
+      <c r="N11">
+        <v>8</v>
+      </c>
+      <c r="O11">
+        <v>92</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>30.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>7.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>7.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>13.166666666666668</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>80</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>34</v>
+      </c>
+      <c r="E12">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>88</v>
+      </c>
+      <c r="H12">
+        <v>12</v>
+      </c>
+      <c r="I12">
+        <v>35</v>
+      </c>
+      <c r="J12">
+        <v>65</v>
+      </c>
+      <c r="L12">
+        <v>94</v>
+      </c>
+      <c r="M12">
+        <v>6</v>
+      </c>
+      <c r="N12">
+        <v>12</v>
+      </c>
+      <c r="O12">
+        <v>88</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>23.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>10.833333333333332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>68</v>
+      </c>
+      <c r="C13">
+        <v>32</v>
+      </c>
+      <c r="D13">
+        <v>29</v>
+      </c>
+      <c r="E13">
+        <v>71</v>
+      </c>
+      <c r="G13">
+        <v>74</v>
+      </c>
+      <c r="H13">
+        <v>26</v>
+      </c>
+      <c r="I13">
+        <v>44</v>
+      </c>
+      <c r="J13">
+        <v>56</v>
+      </c>
+      <c r="L13">
+        <v>94</v>
+      </c>
+      <c r="M13">
+        <v>6</v>
+      </c>
+      <c r="N13">
+        <v>17</v>
+      </c>
+      <c r="O13">
+        <v>83</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>30.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>11.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>25.666666666666668</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>14.166666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -11388,19 +11781,19 @@
         <v>91</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q11:Q14" si="6">AVERAGE(C12,D12)</f>
+        <f t="shared" ref="Q12:Q14" si="6">AVERAGE(C12,D12)</f>
         <v>24.5</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R11:R14" si="7">AVERAGE(H12,I12)</f>
+        <f t="shared" ref="R12:R14" si="7">AVERAGE(H12,I12)</f>
         <v>24.5</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S11:S14" si="8">AVERAGE(M12,N12)</f>
+        <f t="shared" ref="S12:S14" si="8">AVERAGE(M12,N12)</f>
         <v>11</v>
       </c>
       <c r="T12">
-        <f t="shared" ref="T11:T14" si="9">AVERAGE(Q12:S12)</f>
+        <f t="shared" ref="T12:T14" si="9">AVERAGE(Q12:S12)</f>
         <v>20</v>
       </c>
       <c r="U12">
@@ -11436,11 +11829,11 @@
         <v>1.1706281947614148</v>
       </c>
       <c r="AC12">
-        <f t="shared" ref="AC11:AC14" si="10">MIN(Q12:S12)</f>
+        <f t="shared" ref="AC12:AC14" si="10">MIN(Q12:S12)</f>
         <v>11</v>
       </c>
       <c r="AD12">
-        <f t="shared" ref="AD11:AD14" si="11">(T12-AC12)</f>
+        <f t="shared" ref="AD12:AD14" si="11">(T12-AC12)</f>
         <v>9</v>
       </c>
       <c r="AE12">

--- a/DataAnalysis/LT/0.05/Results.xlsx
+++ b/DataAnalysis/LT/0.05/Results.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LT\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E907A2-3BD4-4730-AFC9-5EC06CA68C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA1DBF0-1383-42B9-A182-122B8D34C819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
     <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
+    <sheet name="PARBS_STDAUG" sheetId="18" r:id="rId3"/>
     <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
     <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
     <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId6"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="77">
   <si>
     <t>Dati originali</t>
   </si>
@@ -600,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1085,166 +1085,303 @@
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
+      <c r="F21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21">
+        <v>27.416666666666668</v>
+      </c>
+      <c r="H21">
+        <v>2.083666640004266</v>
+      </c>
+      <c r="I21">
+        <v>28.583333333333332</v>
+      </c>
+      <c r="J21">
+        <v>3.292668623877387</v>
+      </c>
+      <c r="K21">
+        <v>8.5</v>
+      </c>
+      <c r="L21">
+        <v>1.8973665961010275</v>
+      </c>
+      <c r="M21">
+        <v>21.500000000000004</v>
+      </c>
+      <c r="N21">
+        <v>1.2560962454277844</v>
+      </c>
+      <c r="O21">
+        <v>13</v>
+      </c>
+      <c r="P21">
+        <v>2.0357908646136602</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E22" t="s">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
         <v>68</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>31.875</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>2.2867371223353739</v>
       </c>
-      <c r="I22">
+      <c r="I23">
         <v>27.5</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>3.5590260840104371</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>8.125</v>
       </c>
-      <c r="L22">
+      <c r="L23">
         <v>2.056493779875511</v>
       </c>
-      <c r="M22">
+      <c r="M23">
         <v>22.5</v>
       </c>
-      <c r="N22">
+      <c r="N23">
         <v>1.3402597868683137</v>
       </c>
-      <c r="O22">
+      <c r="O23">
         <v>14.375</v>
       </c>
-      <c r="P22">
+      <c r="P23">
         <v>2.532657073480697</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="G24">
+        <v>29.625</v>
+      </c>
+      <c r="H24">
+        <v>2.6259918760981216</v>
+      </c>
+      <c r="I24">
+        <v>27.375</v>
+      </c>
+      <c r="J24">
+        <v>5.0559371040391712</v>
+      </c>
+      <c r="K24">
+        <v>11</v>
+      </c>
+      <c r="L24">
+        <v>0.40824829046386302</v>
+      </c>
+      <c r="M24">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="N24">
+        <v>2.1125725935368393</v>
+      </c>
+      <c r="O24">
+        <v>11.666666666666668</v>
+      </c>
+      <c r="P24">
+        <v>2.4645636680909782</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>23.833333333333332</v>
-      </c>
-      <c r="H25">
-        <v>3.6968455021364766</v>
-      </c>
-      <c r="I25">
-        <v>22</v>
-      </c>
-      <c r="J25">
-        <v>3.03315017762062</v>
-      </c>
-      <c r="K25">
-        <v>8.5833333333333339</v>
-      </c>
-      <c r="L25">
-        <v>1.9853631070075477</v>
-      </c>
-      <c r="M25">
-        <v>18.138888888888889</v>
-      </c>
-      <c r="N25">
-        <v>2.2959303770576787</v>
-      </c>
-      <c r="O25">
-        <v>9.5555555555555554</v>
-      </c>
-      <c r="P25">
-        <v>1.9254629073050034</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26">
-        <v>18.666666666666668</v>
-      </c>
-      <c r="H26">
-        <v>5.9651767227244301</v>
-      </c>
-      <c r="I26">
-        <v>19.333333333333332</v>
-      </c>
-      <c r="J26">
-        <v>3.6855573979160021</v>
-      </c>
-      <c r="K26">
-        <v>10.5</v>
-      </c>
-      <c r="L26">
-        <v>0.5</v>
-      </c>
-      <c r="M26">
-        <v>16.166666666666668</v>
-      </c>
-      <c r="N26">
-        <v>3.3706247360261101</v>
-      </c>
-      <c r="O26">
-        <v>5.666666666666667</v>
-      </c>
-      <c r="P26">
-        <v>2.9059326290271166</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>23.833333333333332</v>
+      </c>
+      <c r="H27">
+        <v>3.6968455021364766</v>
+      </c>
+      <c r="I27">
+        <v>22</v>
+      </c>
+      <c r="J27">
+        <v>3.03315017762062</v>
+      </c>
+      <c r="K27">
+        <v>8.5833333333333339</v>
+      </c>
+      <c r="L27">
+        <v>1.9853631070075477</v>
+      </c>
+      <c r="M27">
+        <v>18.138888888888889</v>
+      </c>
+      <c r="N27">
+        <v>2.2959303770576787</v>
+      </c>
+      <c r="O27">
+        <v>9.5555555555555554</v>
+      </c>
+      <c r="P27">
+        <v>1.9254629073050034</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>18.666666666666668</v>
+      </c>
+      <c r="H28">
+        <v>5.9651767227244301</v>
+      </c>
+      <c r="I28">
+        <v>19.333333333333332</v>
+      </c>
+      <c r="J28">
+        <v>3.6855573979160021</v>
+      </c>
+      <c r="K28">
+        <v>10.5</v>
+      </c>
+      <c r="L28">
+        <v>0.5</v>
+      </c>
+      <c r="M28">
+        <v>16.166666666666668</v>
+      </c>
+      <c r="N28">
+        <v>3.3706247360261101</v>
+      </c>
+      <c r="O28">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="P28">
+        <v>2.9059326290271166</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30">
+        <v>23.5</v>
+      </c>
+      <c r="H30">
+        <v>5.634713834792322</v>
+      </c>
+      <c r="I30">
+        <v>22.5</v>
+      </c>
+      <c r="J30">
+        <v>5.4083269131959844</v>
+      </c>
+      <c r="K30">
+        <v>7</v>
+      </c>
+      <c r="L30">
+        <v>2.2912878474779199</v>
+      </c>
+      <c r="M30">
+        <v>17.666666666666668</v>
+      </c>
+      <c r="N30">
+        <v>4.3429380735984644</v>
+      </c>
+      <c r="O30">
+        <v>3.5555555555555558</v>
+      </c>
+      <c r="P30">
+        <v>0.80699105812966365</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E29" t="s">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E32" t="s">
         <v>68</v>
       </c>
-      <c r="G29">
+      <c r="G32">
         <v>21.5</v>
       </c>
-      <c r="H29">
+      <c r="H32">
         <v>4.5</v>
       </c>
-      <c r="I29">
+      <c r="I32">
         <v>22.666666666666668</v>
       </c>
-      <c r="J29">
+      <c r="J32">
         <v>3.8188130791298716</v>
       </c>
-      <c r="K29">
+      <c r="K32">
         <v>10.666666666666666</v>
       </c>
-      <c r="L29">
+      <c r="L32">
         <v>0.28867513459481292</v>
       </c>
-      <c r="M29">
+      <c r="M32">
         <v>18.277777777777775</v>
       </c>
-      <c r="N29">
+      <c r="N32">
         <v>2.3589859717291444</v>
       </c>
-      <c r="O29">
+      <c r="O32">
         <v>7.6111111111111107</v>
       </c>
-      <c r="P29">
+      <c r="P32">
         <v>2.0705161281760218</v>
+      </c>
+    </row>
+    <row r="33" spans="6:16" x14ac:dyDescent="0.3">
+      <c r="F33" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="H33">
+        <v>3.7859388972001873</v>
+      </c>
+      <c r="I33">
+        <v>20.833333333333332</v>
+      </c>
+      <c r="J33">
+        <v>4.2524502740576953</v>
+      </c>
+      <c r="K33">
+        <v>11.166666666666666</v>
+      </c>
+      <c r="L33">
+        <v>1.0408329997330665</v>
+      </c>
+      <c r="M33">
+        <v>18.222222222222225</v>
+      </c>
+      <c r="N33">
+        <v>2.2750661366047948</v>
+      </c>
+      <c r="O33">
+        <v>7.0555555555555562</v>
+      </c>
+      <c r="P33">
+        <v>3.3096380019125498</v>
       </c>
     </row>
   </sheetData>
@@ -5636,19 +5773,19 @@
         <v>93</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C9,D9)</f>
+        <f t="shared" ref="Q9:Q13" si="6">AVERAGE(C9,D9)</f>
         <v>24</v>
       </c>
       <c r="R9">
-        <f t="shared" ref="R8:R13" si="7">AVERAGE(H9,I9)</f>
+        <f t="shared" ref="R9:R13" si="7">AVERAGE(H9,I9)</f>
         <v>23.5</v>
       </c>
       <c r="S9">
-        <f t="shared" ref="S8:S13" si="8">AVERAGE(M9,N9)</f>
+        <f t="shared" ref="S9:S13" si="8">AVERAGE(M9,N9)</f>
         <v>10.5</v>
       </c>
       <c r="T9">
-        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q9:S9)</f>
+        <f t="shared" ref="T9:T13" si="9">AVERAGE(Q9:S9)</f>
         <v>19.333333333333332</v>
       </c>
       <c r="U9">
@@ -5684,11 +5821,11 @@
         <v>0.55067298893330685</v>
       </c>
       <c r="AC9">
-        <f t="shared" ref="AC8:AC13" si="10">MIN(Q9:S9)</f>
+        <f t="shared" ref="AC9:AC13" si="10">MIN(Q9:S9)</f>
         <v>10.5</v>
       </c>
       <c r="AD9">
-        <f t="shared" ref="AD8:AD13" si="11">(T9-AC9)</f>
+        <f t="shared" ref="AD9:AD13" si="11">(T9-AC9)</f>
         <v>8.8333333333333321</v>
       </c>
       <c r="AE9">
@@ -10361,7 +10498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -10717,6 +10854,299 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>17.666666666666668</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>70</v>
+      </c>
+      <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>37</v>
+      </c>
+      <c r="E12">
+        <v>63</v>
+      </c>
+      <c r="G12">
+        <v>76</v>
+      </c>
+      <c r="H12">
+        <v>24</v>
+      </c>
+      <c r="I12">
+        <v>39</v>
+      </c>
+      <c r="J12">
+        <v>61</v>
+      </c>
+      <c r="L12">
+        <v>95</v>
+      </c>
+      <c r="M12">
+        <v>5</v>
+      </c>
+      <c r="N12">
+        <v>16</v>
+      </c>
+      <c r="O12">
+        <v>84</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q8:Q15" si="6">AVERAGE(C12,D12)</f>
+        <v>33.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R8:R15" si="7">AVERAGE(H12,I12)</f>
+        <v>31.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S8:S15" si="8">AVERAGE(M12,N12)</f>
+        <v>10.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T8:T15" si="9">AVERAGE(Q12:S12)</f>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="U12">
+        <f>AVERAGE(Q12:Q15)</f>
+        <v>29.625</v>
+      </c>
+      <c r="V12">
+        <f>_xlfn.STDEV.S(Q12:Q15)</f>
+        <v>2.6259918760981216</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(R12:R15)</f>
+        <v>27.375</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(R12:R15)</f>
+        <v>5.0559371040391712</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(S12:S15)</f>
+        <v>11</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(S12:S15)</f>
+        <v>0.40824829046386302</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(T12:T15)</f>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(T12:T15)</f>
+        <v>2.1125725935368393</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" ref="AC8:AC15" si="10">MIN(Q12:S12)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" ref="AD8:AD15" si="11">(T12-AC12)</f>
+        <v>14.666666666666668</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(AD12:AD15)</f>
+        <v>11.666666666666668</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(AD12:AD15)</f>
+        <v>2.4645636680909782</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>71</v>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>27</v>
+      </c>
+      <c r="E13">
+        <v>73</v>
+      </c>
+      <c r="G13">
+        <v>89</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>35</v>
+      </c>
+      <c r="J13">
+        <v>65</v>
+      </c>
+      <c r="L13">
+        <v>87</v>
+      </c>
+      <c r="M13">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>90</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>11.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>9.3333333333333321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>65</v>
+      </c>
+      <c r="C14">
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <v>23</v>
+      </c>
+      <c r="E14">
+        <v>77</v>
+      </c>
+      <c r="G14">
+        <v>85</v>
+      </c>
+      <c r="H14">
+        <v>15</v>
+      </c>
+      <c r="I14">
+        <v>31</v>
+      </c>
+      <c r="J14">
+        <v>69</v>
+      </c>
+      <c r="L14">
+        <v>87</v>
+      </c>
+      <c r="M14">
+        <v>13</v>
+      </c>
+      <c r="N14">
+        <v>9</v>
+      </c>
+      <c r="O14">
+        <v>91</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>21</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>68</v>
+      </c>
+      <c r="C15">
+        <v>32</v>
+      </c>
+      <c r="D15">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>76</v>
+      </c>
+      <c r="G15">
+        <v>76</v>
+      </c>
+      <c r="H15">
+        <v>24</v>
+      </c>
+      <c r="I15">
+        <v>40</v>
+      </c>
+      <c r="J15">
+        <v>60</v>
+      </c>
+      <c r="L15">
+        <v>93</v>
+      </c>
+      <c r="M15">
+        <v>7</v>
+      </c>
+      <c r="N15">
+        <v>15</v>
+      </c>
+      <c r="O15">
+        <v>85</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="7"/>
+        <v>32</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="8"/>
+        <v>11</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="9"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="11"/>
+        <v>12.666666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -10726,7 +11156,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
-  <dimension ref="A2:AF5"/>
+  <dimension ref="A2:AF6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -10794,95 +11224,229 @@
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q4" t="e">
+      <c r="B4">
+        <v>68</v>
+      </c>
+      <c r="C4">
+        <v>32</v>
+      </c>
+      <c r="D4">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>72</v>
+      </c>
+      <c r="G4">
+        <v>88</v>
+      </c>
+      <c r="H4">
+        <v>12</v>
+      </c>
+      <c r="I4">
+        <v>45</v>
+      </c>
+      <c r="J4">
+        <v>55</v>
+      </c>
+      <c r="L4">
+        <v>93</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
+      </c>
+      <c r="N4">
+        <v>12</v>
+      </c>
+      <c r="O4">
+        <v>88</v>
+      </c>
+      <c r="Q4">
         <f>AVERAGE(C4,D4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" t="e">
+        <v>30</v>
+      </c>
+      <c r="R4">
         <f>AVERAGE(H4,I4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S4" t="e">
+        <v>28.5</v>
+      </c>
+      <c r="S4">
         <f>AVERAGE(M4,N4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T4" t="e">
+        <v>9.5</v>
+      </c>
+      <c r="T4">
         <f>AVERAGE(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" t="e">
-        <f>AVERAGE(Q4,Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" t="e">
-        <f>_xlfn.STDEV.S(Q4,Q5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W4" t="e">
-        <f>AVERAGE(R4,R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X4" t="e">
-        <f>_xlfn.STDEV.S(R4,R5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y4" t="e">
-        <f>AVERAGE(S4,S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z4" t="e">
-        <f>_xlfn.STDEV.S(S4,S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA4" t="e">
-        <f>AVERAGE(T4,T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB4" t="e">
-        <f>_xlfn.STDEV.S(T4,T5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC4" t="e">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4,Q5:Q6)</f>
+        <v>23.5</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4,Q5:Q6)</f>
+        <v>5.634713834792322</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4,R5:R6)</f>
+        <v>22.5</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4,R5:R6)</f>
+        <v>5.4083269131959844</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4,S5:S6)</f>
+        <v>7</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4,S5:S6)</f>
+        <v>2.2912878474779199</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4,T5:T6)</f>
+        <v>17.666666666666668</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4,T5:T6)</f>
+        <v>4.3429380735984644</v>
+      </c>
+      <c r="AC4">
         <f>MIN(Q4:S4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD4" t="e">
+        <v>9.5</v>
+      </c>
+      <c r="AD4">
         <f>(1/3)*(T4-AC4)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE4" t="e">
-        <f>AVERAGE(AD4,AD5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF4" t="e">
-        <f>_xlfn.STDEV.S(AD4,AD5)</f>
-        <v>#DIV/0!</v>
+        <v>4.3888888888888893</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4,AD5:AD6)</f>
+        <v>3.5555555555555558</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4,AD5:AD6)</f>
+        <v>0.80699105812966365</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="Q5" t="e">
+      <c r="B5">
+        <v>82</v>
+      </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
+      <c r="D5">
+        <v>22</v>
+      </c>
+      <c r="E5">
+        <v>78</v>
+      </c>
+      <c r="G5">
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>74</v>
+      </c>
+      <c r="L5">
+        <v>97</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5">
+        <v>10</v>
+      </c>
+      <c r="O5">
+        <v>90</v>
+      </c>
+      <c r="Q5">
         <f>AVERAGE(C5,D5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" t="e">
+        <v>20</v>
+      </c>
+      <c r="R5">
         <f>AVERAGE(H5,I5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S5" t="e">
+        <v>18</v>
+      </c>
+      <c r="S5">
         <f>AVERAGE(M5,N5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T5" t="e">
+        <v>6.5</v>
+      </c>
+      <c r="T5">
         <f>AVERAGE(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC5" t="e">
+        <v>14.833333333333334</v>
+      </c>
+      <c r="AC5">
         <f>MIN(Q5:S5)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD5" t="e">
+        <v>6.5</v>
+      </c>
+      <c r="AD5">
         <f>(1/3)*(T5-AC5)</f>
-        <v>#DIV/0!</v>
+        <v>2.7777777777777777</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>15</v>
+      </c>
+      <c r="D6">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>74</v>
+      </c>
+      <c r="G6">
+        <v>94</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>36</v>
+      </c>
+      <c r="J6">
+        <v>64</v>
+      </c>
+      <c r="L6">
+        <v>96</v>
+      </c>
+      <c r="M6">
+        <v>4</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="O6">
+        <v>94</v>
+      </c>
+      <c r="Q6">
+        <f>AVERAGE(C6,D6)</f>
+        <v>20.5</v>
+      </c>
+      <c r="R6">
+        <f>AVERAGE(H6,I6)</f>
+        <v>21</v>
+      </c>
+      <c r="S6">
+        <f>AVERAGE(M6,N6)</f>
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <f>AVERAGE(Q6:S6)</f>
+        <v>15.5</v>
+      </c>
+      <c r="AC6">
+        <f>MIN(Q6:S6)</f>
+        <v>5</v>
+      </c>
+      <c r="AD6">
+        <f>(1/3)*(T6-AC6)</f>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -10892,7 +11456,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11188,6 +11752,237 @@
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>80</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <v>93</v>
+      </c>
+      <c r="H12">
+        <v>7</v>
+      </c>
+      <c r="I12">
+        <v>26</v>
+      </c>
+      <c r="J12">
+        <v>74</v>
+      </c>
+      <c r="L12">
+        <v>91</v>
+      </c>
+      <c r="M12">
+        <v>9</v>
+      </c>
+      <c r="N12">
+        <v>15</v>
+      </c>
+      <c r="O12">
+        <v>85</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q7:Q14" si="6">AVERAGE(C12:D12)</f>
+        <v>20</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R7:R14" si="7">AVERAGE(H12:I12)</f>
+        <v>16.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S7:S14" si="8">AVERAGE(M12:N12)</f>
+        <v>12</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T7:T14" si="9">AVERAGE(Q12:S12)</f>
+        <v>16.166666666666668</v>
+      </c>
+      <c r="U12">
+        <f>AVERAGE(Q12:Q14)</f>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="V12">
+        <f>_xlfn.STDEV.S(Q12:Q14)</f>
+        <v>3.7859388972001873</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(R12:R14)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(R12:R14)</f>
+        <v>4.2524502740576953</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(S12:S14)</f>
+        <v>11.166666666666666</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(S12:S14)</f>
+        <v>1.0408329997330665</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(T12:T14)</f>
+        <v>18.222222222222225</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(T12:T14)</f>
+        <v>2.2750661366047948</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" ref="AC7:AC14" si="10">MIN(Q12:S12)</f>
+        <v>12</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" ref="AD7:AD14" si="11">T12-AC12</f>
+        <v>4.1666666666666679</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(AD12:AD14)</f>
+        <v>7.0555555555555562</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(AD12:AD14)</f>
+        <v>3.3096380019125498</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>78</v>
+      </c>
+      <c r="C13">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>87</v>
+      </c>
+      <c r="H13">
+        <v>13</v>
+      </c>
+      <c r="I13">
+        <v>29</v>
+      </c>
+      <c r="J13">
+        <v>71</v>
+      </c>
+      <c r="L13">
+        <v>92</v>
+      </c>
+      <c r="M13">
+        <v>8</v>
+      </c>
+      <c r="N13">
+        <v>15</v>
+      </c>
+      <c r="O13">
+        <v>85</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>21</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>11.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>11.5</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>6.3333333333333321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>35</v>
+      </c>
+      <c r="E14">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>86</v>
+      </c>
+      <c r="H14">
+        <v>14</v>
+      </c>
+      <c r="I14">
+        <v>36</v>
+      </c>
+      <c r="J14">
+        <v>64</v>
+      </c>
+      <c r="L14">
+        <v>88</v>
+      </c>
+      <c r="M14">
+        <v>12</v>
+      </c>
+      <c r="N14">
+        <v>8</v>
+      </c>
+      <c r="O14">
+        <v>92</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>27</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>10.666666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -11197,7 +11992,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF14"/>
+  <dimension ref="A2:AF26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11967,6 +12762,423 @@
       <c r="AD14">
         <f t="shared" si="11"/>
         <v>10.333333333333332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>78</v>
+      </c>
+      <c r="C21">
+        <v>22</v>
+      </c>
+      <c r="D21">
+        <v>32</v>
+      </c>
+      <c r="E21">
+        <v>68</v>
+      </c>
+      <c r="G21">
+        <v>87</v>
+      </c>
+      <c r="H21">
+        <v>13</v>
+      </c>
+      <c r="I21">
+        <v>49</v>
+      </c>
+      <c r="J21">
+        <v>51</v>
+      </c>
+      <c r="L21">
+        <v>86</v>
+      </c>
+      <c r="M21">
+        <v>14</v>
+      </c>
+      <c r="N21">
+        <v>6</v>
+      </c>
+      <c r="O21">
+        <v>94</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" ref="Q15:Q26" si="12">AVERAGE(C21,D21)</f>
+        <v>27</v>
+      </c>
+      <c r="R21">
+        <f t="shared" ref="R15:R26" si="13">AVERAGE(H21,I21)</f>
+        <v>31</v>
+      </c>
+      <c r="S21">
+        <f t="shared" ref="S15:S26" si="14">AVERAGE(M21,N21)</f>
+        <v>10</v>
+      </c>
+      <c r="T21">
+        <f t="shared" ref="T15:T26" si="15">AVERAGE(Q21:S21)</f>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="U21">
+        <f>AVERAGE(Q21:Q27)</f>
+        <v>27.416666666666668</v>
+      </c>
+      <c r="V21">
+        <f>_xlfn.STDEV.S(Q21:Q27)</f>
+        <v>2.083666640004266</v>
+      </c>
+      <c r="W21">
+        <f>AVERAGE(R21:R27)</f>
+        <v>28.583333333333332</v>
+      </c>
+      <c r="X21">
+        <f>_xlfn.STDEV.S(R21:R27)</f>
+        <v>3.292668623877387</v>
+      </c>
+      <c r="Y21">
+        <f>AVERAGE(S21:S27)</f>
+        <v>8.5</v>
+      </c>
+      <c r="Z21">
+        <f>_xlfn.STDEV.S(S21:S27)</f>
+        <v>1.8973665961010275</v>
+      </c>
+      <c r="AA21">
+        <f>AVERAGE(T21:T27)</f>
+        <v>21.500000000000004</v>
+      </c>
+      <c r="AB21">
+        <f>_xlfn.STDEV.S(T21:T27)</f>
+        <v>1.2560962454277844</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" ref="AC15:AC26" si="16">MIN(Q21:S21)</f>
+        <v>10</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" ref="AD15:AD26" si="17">(T21-AC21)</f>
+        <v>12.666666666666668</v>
+      </c>
+      <c r="AE21">
+        <f>AVERAGE(AD21:AD27)</f>
+        <v>13</v>
+      </c>
+      <c r="AF21">
+        <f>_xlfn.STDEV.S(AD21:AD27)</f>
+        <v>2.0357908646136602</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>67</v>
+      </c>
+      <c r="C22">
+        <v>33</v>
+      </c>
+      <c r="D22">
+        <v>28</v>
+      </c>
+      <c r="E22">
+        <v>72</v>
+      </c>
+      <c r="G22">
+        <v>82</v>
+      </c>
+      <c r="H22">
+        <v>18</v>
+      </c>
+      <c r="I22">
+        <v>43</v>
+      </c>
+      <c r="J22">
+        <v>57</v>
+      </c>
+      <c r="L22">
+        <v>93</v>
+      </c>
+      <c r="M22">
+        <v>7</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22">
+        <v>97</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="12"/>
+        <v>30.5</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="13"/>
+        <v>30.5</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="15"/>
+        <v>22</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="17"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>84</v>
+      </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>36</v>
+      </c>
+      <c r="E23">
+        <v>64</v>
+      </c>
+      <c r="G23">
+        <v>88</v>
+      </c>
+      <c r="H23">
+        <v>12</v>
+      </c>
+      <c r="I23">
+        <v>47</v>
+      </c>
+      <c r="J23">
+        <v>53</v>
+      </c>
+      <c r="L23">
+        <v>96</v>
+      </c>
+      <c r="M23">
+        <v>4</v>
+      </c>
+      <c r="N23">
+        <v>15</v>
+      </c>
+      <c r="O23">
+        <v>85</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="13"/>
+        <v>29.5</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="14"/>
+        <v>9.5</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="15"/>
+        <v>21.666666666666668</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="16"/>
+        <v>9.5</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="17"/>
+        <v>12.166666666666668</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>71</v>
+      </c>
+      <c r="C24">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
+      <c r="E24">
+        <v>70</v>
+      </c>
+      <c r="G24">
+        <v>86</v>
+      </c>
+      <c r="H24">
+        <v>14</v>
+      </c>
+      <c r="I24">
+        <v>37</v>
+      </c>
+      <c r="J24">
+        <v>63</v>
+      </c>
+      <c r="L24">
+        <v>95</v>
+      </c>
+      <c r="M24">
+        <v>5</v>
+      </c>
+      <c r="N24">
+        <v>12</v>
+      </c>
+      <c r="O24">
+        <v>88</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="12"/>
+        <v>29.5</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="13"/>
+        <v>25.5</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="14"/>
+        <v>8.5</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="15"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="16"/>
+        <v>8.5</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" si="17"/>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>75</v>
+      </c>
+      <c r="C25">
+        <v>25</v>
+      </c>
+      <c r="D25">
+        <v>27</v>
+      </c>
+      <c r="E25">
+        <v>73</v>
+      </c>
+      <c r="G25">
+        <v>85</v>
+      </c>
+      <c r="H25">
+        <v>15</v>
+      </c>
+      <c r="I25">
+        <v>32</v>
+      </c>
+      <c r="J25">
+        <v>68</v>
+      </c>
+      <c r="L25">
+        <v>92</v>
+      </c>
+      <c r="M25">
+        <v>8</v>
+      </c>
+      <c r="N25">
+        <v>8</v>
+      </c>
+      <c r="O25">
+        <v>92</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="13"/>
+        <v>23.5</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="14"/>
+        <v>8</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="15"/>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="16"/>
+        <v>8</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="17"/>
+        <v>11.166666666666668</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>72</v>
+      </c>
+      <c r="C26">
+        <v>28</v>
+      </c>
+      <c r="D26">
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>77</v>
+      </c>
+      <c r="G26">
+        <v>80</v>
+      </c>
+      <c r="H26">
+        <v>20</v>
+      </c>
+      <c r="I26">
+        <v>43</v>
+      </c>
+      <c r="J26">
+        <v>57</v>
+      </c>
+      <c r="L26">
+        <v>92</v>
+      </c>
+      <c r="M26">
+        <v>8</v>
+      </c>
+      <c r="N26">
+        <v>12</v>
+      </c>
+      <c r="O26">
+        <v>88</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="12"/>
+        <v>25.5</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="13"/>
+        <v>31.5</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="14"/>
+        <v>10</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="15"/>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="17"/>
+        <v>12.333333333333332</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/LT/0.05/Results.xlsx
+++ b/DataAnalysis/LT/0.05/Results.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LT\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA1DBF0-1383-42B9-A182-122B8D34C819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAD4F67-C8E8-49C7-B619-A51DC72E928D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="PARBS_STDAUG" sheetId="18" r:id="rId3"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId6"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId7"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId8"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId9"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId11"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId12"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId13"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId15"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId16"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId17"/>
+    <sheet name="DIFF_ONLYMIN" sheetId="20" r:id="rId2"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
+    <sheet name="PARBS_STDAUG" sheetId="18" r:id="rId4"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId8"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId9"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId10"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId11"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="77">
   <si>
     <t>Dati originali</t>
   </si>
@@ -600,13 +601,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -641,12 +642,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>4</v>
       </c>
@@ -680,8 +681,11 @@
       <c r="P3">
         <v>0.53575837561071948</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>2</v>
       </c>
@@ -718,18 +722,48 @@
       <c r="P4">
         <v>1.4174834246858978</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R4">
+        <v>29.5</v>
+      </c>
+      <c r="S4">
+        <v>4.9497474683058327</v>
+      </c>
+      <c r="T4">
+        <v>28.25</v>
+      </c>
+      <c r="U4">
+        <v>6.0104076400856536</v>
+      </c>
+      <c r="V4">
+        <v>9.25</v>
+      </c>
+      <c r="W4">
+        <v>5.3033008588991066</v>
+      </c>
+      <c r="X4">
+        <v>22.333333333333336</v>
+      </c>
+      <c r="Y4">
+        <v>5.4211519890968356</v>
+      </c>
+      <c r="Z4">
+        <v>13.083333333333334</v>
+      </c>
+      <c r="AA4">
+        <v>0.11785113019775875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
         <v>43</v>
       </c>
@@ -767,12 +801,12 @@
         <v>2.8284271247461903</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
         <v>43</v>
       </c>
@@ -810,7 +844,7 @@
         <v>1.2963624321753362</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>52</v>
       </c>
@@ -845,7 +879,7 @@
         <v>0.72008229982309568</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>76</v>
       </c>
@@ -880,507 +914,583 @@
         <v>1.9340994650588066</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13">
+        <v>30.666666666666668</v>
+      </c>
+      <c r="H13">
+        <v>1.0408329997330663</v>
+      </c>
+      <c r="I13">
+        <v>30</v>
+      </c>
+      <c r="J13">
+        <v>4.7696960070847281</v>
+      </c>
+      <c r="K13">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="L13">
+        <v>1.8929694486000899</v>
+      </c>
+      <c r="M13">
+        <v>23.111111111111111</v>
+      </c>
+      <c r="N13">
+        <v>1.9883922409081429</v>
+      </c>
+      <c r="O13">
+        <v>14.444444444444443</v>
+      </c>
+      <c r="P13">
+        <v>0.5091750772173157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
         <v>4</v>
       </c>
-      <c r="G13">
+      <c r="G16">
         <v>31.8</v>
       </c>
-      <c r="H13">
+      <c r="H16">
         <v>3.4496376621320741</v>
       </c>
-      <c r="I13">
+      <c r="I16">
         <v>30.25</v>
       </c>
-      <c r="J13">
+      <c r="J16">
         <v>3.2850672240711707</v>
       </c>
-      <c r="K13">
+      <c r="K16">
         <v>12.25</v>
       </c>
-      <c r="L13">
+      <c r="L16">
         <v>1.7677669529663689</v>
       </c>
-      <c r="M13">
+      <c r="M16">
         <v>24.766666666666666</v>
       </c>
-      <c r="N13">
+      <c r="N16">
         <v>1.4890547171334187</v>
       </c>
-      <c r="O13">
+      <c r="O16">
         <v>12.516666666666666</v>
       </c>
-      <c r="P13">
+      <c r="P16">
         <v>1.8026900338174325</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F17" t="s">
         <v>21</v>
       </c>
-      <c r="G14">
+      <c r="G17">
         <v>29.5625</v>
       </c>
-      <c r="H14">
+      <c r="H17">
         <v>4.8361547594284922</v>
       </c>
-      <c r="I14">
+      <c r="I17">
         <v>26</v>
       </c>
-      <c r="J14">
+      <c r="J17">
         <v>4.5747755604588329</v>
       </c>
-      <c r="K14">
+      <c r="K17">
         <v>11.1875</v>
       </c>
-      <c r="L14">
+      <c r="L17">
         <v>2.2509918448795601</v>
       </c>
-      <c r="M14">
+      <c r="M17">
         <v>22.25</v>
       </c>
-      <c r="N14">
+      <c r="N17">
         <v>2.8702082220799161</v>
       </c>
-      <c r="O14">
+      <c r="O17">
         <v>11.062499999999998</v>
       </c>
-      <c r="P14">
+      <c r="P17">
         <v>3.1896876246518548</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>4</v>
       </c>
-      <c r="G17">
+      <c r="G20">
         <v>36.642857142857146</v>
       </c>
-      <c r="H17">
+      <c r="H20">
         <v>4.9135381491199581</v>
       </c>
-      <c r="I17">
+      <c r="I20">
         <v>32.5</v>
       </c>
-      <c r="J17">
+      <c r="J20">
         <v>4.9413223601245315</v>
       </c>
-      <c r="K17">
+      <c r="K20">
         <v>11</v>
       </c>
-      <c r="L17">
+      <c r="L20">
         <v>1.9148542155126762</v>
       </c>
-      <c r="M17">
+      <c r="M20">
         <v>26.714285714285712</v>
       </c>
-      <c r="N17">
+      <c r="N20">
         <v>3.0470299529856346</v>
       </c>
-      <c r="O17">
+      <c r="O20">
         <v>15.714285714285714</v>
       </c>
-      <c r="P17">
+      <c r="P20">
         <v>3.5207247329921398</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
         <v>68</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F21" t="s">
         <v>21</v>
       </c>
-      <c r="G18">
+      <c r="G21">
         <v>27.25</v>
       </c>
-      <c r="H18">
+      <c r="H21">
         <v>4.6124830622995248</v>
       </c>
-      <c r="I18">
+      <c r="I21">
         <v>27.833333333333332</v>
       </c>
-      <c r="J18">
+      <c r="J21">
         <v>2.9944392908634274</v>
       </c>
-      <c r="K18">
+      <c r="K21">
         <v>10.416666666666666</v>
       </c>
-      <c r="L18">
+      <c r="L21">
         <v>2.8533605917701106</v>
       </c>
-      <c r="M18">
+      <c r="M21">
         <v>21.833333333333332</v>
       </c>
-      <c r="N18">
+      <c r="N21">
         <v>2.3452078799117149</v>
       </c>
-      <c r="O18">
+      <c r="O21">
         <v>11.416666666666664</v>
       </c>
-      <c r="P18">
+      <c r="P21">
         <v>3.2158461820595017</v>
       </c>
-    </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
+      <c r="Q21" t="s">
+        <v>76</v>
+      </c>
+      <c r="R21">
+        <v>27.25</v>
+      </c>
+      <c r="S21">
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="T21">
+        <v>25.75</v>
+      </c>
+      <c r="U21">
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="V21">
+        <v>9</v>
+      </c>
+      <c r="W21">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="X21">
+        <v>20.6666666666667</v>
+      </c>
+      <c r="Y21">
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="Z21">
+        <v>11.666666666666668</v>
+      </c>
+      <c r="AA21">
+        <v>1.4142135623730951</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
         <v>68</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F23" t="s">
         <v>22</v>
       </c>
-      <c r="G20">
+      <c r="G23">
         <v>25.666666666666668</v>
       </c>
-      <c r="H20">
+      <c r="H23">
         <v>2.9297326385411577</v>
       </c>
-      <c r="I20">
+      <c r="I23">
         <v>27.333333333333332</v>
       </c>
-      <c r="J20">
+      <c r="J23">
         <v>5.3463383107818059</v>
       </c>
-      <c r="K20">
+      <c r="K23">
         <v>10.666666666666666</v>
       </c>
-      <c r="L20">
+      <c r="L23">
         <v>0.57735026918962573</v>
       </c>
-      <c r="M20">
+      <c r="M23">
         <v>21.222222222222218</v>
       </c>
-      <c r="N20">
+      <c r="N23">
         <v>1.1706281947614148</v>
       </c>
-      <c r="O20">
+      <c r="O23">
         <v>10.555555555555555</v>
       </c>
-      <c r="P20">
+      <c r="P23">
         <v>1.677740985615729</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="F21" t="s">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
         <v>76</v>
       </c>
-      <c r="G21">
+      <c r="G24">
         <v>27.416666666666668</v>
       </c>
-      <c r="H21">
+      <c r="H24">
         <v>2.083666640004266</v>
       </c>
-      <c r="I21">
+      <c r="I24">
         <v>28.583333333333332</v>
       </c>
-      <c r="J21">
+      <c r="J24">
         <v>3.292668623877387</v>
       </c>
-      <c r="K21">
+      <c r="K24">
         <v>8.5</v>
       </c>
-      <c r="L21">
+      <c r="L24">
         <v>1.8973665961010275</v>
       </c>
-      <c r="M21">
+      <c r="M24">
         <v>21.500000000000004</v>
       </c>
-      <c r="N21">
+      <c r="N24">
         <v>1.2560962454277844</v>
       </c>
-      <c r="O21">
+      <c r="O24">
         <v>13</v>
       </c>
-      <c r="P21">
+      <c r="P24">
         <v>2.0357908646136602</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E23" t="s">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
         <v>68</v>
       </c>
-      <c r="G23">
+      <c r="G26">
         <v>31.875</v>
       </c>
-      <c r="H23">
+      <c r="H26">
         <v>2.2867371223353739</v>
       </c>
-      <c r="I23">
+      <c r="I26">
         <v>27.5</v>
       </c>
-      <c r="J23">
+      <c r="J26">
         <v>3.5590260840104371</v>
       </c>
-      <c r="K23">
+      <c r="K26">
         <v>8.125</v>
       </c>
-      <c r="L23">
+      <c r="L26">
         <v>2.056493779875511</v>
       </c>
-      <c r="M23">
+      <c r="M26">
         <v>22.5</v>
       </c>
-      <c r="N23">
+      <c r="N26">
         <v>1.3402597868683137</v>
       </c>
-      <c r="O23">
+      <c r="O26">
         <v>14.375</v>
       </c>
-      <c r="P23">
+      <c r="P26">
         <v>2.532657073480697</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="G24">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="G27">
         <v>29.625</v>
       </c>
-      <c r="H24">
+      <c r="H27">
         <v>2.6259918760981216</v>
       </c>
-      <c r="I24">
+      <c r="I27">
         <v>27.375</v>
       </c>
-      <c r="J24">
+      <c r="J27">
         <v>5.0559371040391712</v>
       </c>
-      <c r="K24">
+      <c r="K27">
         <v>11</v>
       </c>
-      <c r="L24">
+      <c r="L27">
         <v>0.40824829046386302</v>
       </c>
-      <c r="M24">
+      <c r="M27">
         <v>22.666666666666668</v>
       </c>
-      <c r="N24">
+      <c r="N27">
         <v>2.1125725935368393</v>
       </c>
-      <c r="O24">
+      <c r="O27">
         <v>11.666666666666668</v>
       </c>
-      <c r="P24">
+      <c r="P27">
         <v>2.4645636680909782</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>4</v>
       </c>
-      <c r="G27">
+      <c r="G30">
         <v>23.833333333333332</v>
       </c>
-      <c r="H27">
+      <c r="H30">
         <v>3.6968455021364766</v>
       </c>
-      <c r="I27">
+      <c r="I30">
         <v>22</v>
       </c>
-      <c r="J27">
+      <c r="J30">
         <v>3.03315017762062</v>
       </c>
-      <c r="K27">
+      <c r="K30">
         <v>8.5833333333333339</v>
       </c>
-      <c r="L27">
+      <c r="L30">
         <v>1.9853631070075477</v>
       </c>
-      <c r="M27">
+      <c r="M30">
         <v>18.138888888888889</v>
       </c>
-      <c r="N27">
+      <c r="N30">
         <v>2.2959303770576787</v>
       </c>
-      <c r="O27">
+      <c r="O30">
         <v>9.5555555555555554</v>
       </c>
-      <c r="P27">
+      <c r="P30">
         <v>1.9254629073050034</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
         <v>68</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F31" t="s">
         <v>21</v>
       </c>
-      <c r="G28">
+      <c r="G31">
         <v>18.666666666666668</v>
       </c>
-      <c r="H28">
+      <c r="H31">
         <v>5.9651767227244301</v>
       </c>
-      <c r="I28">
+      <c r="I31">
         <v>19.333333333333332</v>
       </c>
-      <c r="J28">
+      <c r="J31">
         <v>3.6855573979160021</v>
       </c>
-      <c r="K28">
+      <c r="K31">
         <v>10.5</v>
       </c>
-      <c r="L28">
+      <c r="L31">
         <v>0.5</v>
       </c>
-      <c r="M28">
+      <c r="M31">
         <v>16.166666666666668</v>
       </c>
-      <c r="N28">
+      <c r="N31">
         <v>3.3706247360261101</v>
       </c>
-      <c r="O28">
+      <c r="O31">
         <v>5.666666666666667</v>
       </c>
-      <c r="P28">
+      <c r="P31">
         <v>2.9059326290271166</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="F30" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30">
-        <v>23.5</v>
-      </c>
-      <c r="H30">
-        <v>5.634713834792322</v>
-      </c>
-      <c r="I30">
-        <v>22.5</v>
-      </c>
-      <c r="J30">
-        <v>5.4083269131959844</v>
-      </c>
-      <c r="K30">
-        <v>7</v>
-      </c>
-      <c r="L30">
-        <v>2.2912878474779199</v>
-      </c>
-      <c r="M30">
-        <v>17.666666666666668</v>
-      </c>
-      <c r="N30">
-        <v>4.3429380735984644</v>
-      </c>
-      <c r="O30">
-        <v>3.5555555555555558</v>
-      </c>
-      <c r="P30">
-        <v>0.80699105812966365</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E32" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32">
-        <v>21.5</v>
-      </c>
-      <c r="H32">
-        <v>4.5</v>
-      </c>
-      <c r="I32">
-        <v>22.666666666666668</v>
-      </c>
-      <c r="J32">
-        <v>3.8188130791298716</v>
-      </c>
-      <c r="K32">
-        <v>10.666666666666666</v>
-      </c>
-      <c r="L32">
-        <v>0.28867513459481292</v>
-      </c>
-      <c r="M32">
-        <v>18.277777777777775</v>
-      </c>
-      <c r="N32">
-        <v>2.3589859717291444</v>
-      </c>
-      <c r="O32">
-        <v>7.6111111111111107</v>
-      </c>
-      <c r="P32">
-        <v>2.0705161281760218</v>
-      </c>
-    </row>
-    <row r="33" spans="6:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
       <c r="F33" t="s">
         <v>76</v>
       </c>
       <c r="G33">
+        <v>23.5</v>
+      </c>
+      <c r="H33">
+        <v>5.634713834792322</v>
+      </c>
+      <c r="I33">
+        <v>22.5</v>
+      </c>
+      <c r="J33">
+        <v>5.4083269131959844</v>
+      </c>
+      <c r="K33">
+        <v>7</v>
+      </c>
+      <c r="L33">
+        <v>2.2912878474779199</v>
+      </c>
+      <c r="M33">
+        <v>17.666666666666668</v>
+      </c>
+      <c r="N33">
+        <v>4.3429380735984644</v>
+      </c>
+      <c r="O33">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="P33">
+        <v>2.4209731743889984</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>68</v>
+      </c>
+      <c r="G35">
+        <v>21.5</v>
+      </c>
+      <c r="H35">
+        <v>4.5</v>
+      </c>
+      <c r="I35">
         <v>22.666666666666668</v>
       </c>
-      <c r="H33">
+      <c r="J35">
+        <v>3.8188130791298716</v>
+      </c>
+      <c r="K35">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="L35">
+        <v>0.28867513459481292</v>
+      </c>
+      <c r="M35">
+        <v>18.277777777777775</v>
+      </c>
+      <c r="N35">
+        <v>2.3589859717291444</v>
+      </c>
+      <c r="O35">
+        <v>7.6111111111111107</v>
+      </c>
+      <c r="P35">
+        <v>2.0705161281760218</v>
+      </c>
+    </row>
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36">
+        <v>22.666666666666668</v>
+      </c>
+      <c r="H36">
         <v>3.7859388972001873</v>
       </c>
-      <c r="I33">
+      <c r="I36">
         <v>20.833333333333332</v>
       </c>
-      <c r="J33">
+      <c r="J36">
         <v>4.2524502740576953</v>
       </c>
-      <c r="K33">
+      <c r="K36">
         <v>11.166666666666666</v>
       </c>
-      <c r="L33">
+      <c r="L36">
         <v>1.0408329997330665</v>
       </c>
-      <c r="M33">
+      <c r="M36">
         <v>18.222222222222225</v>
       </c>
-      <c r="N33">
+      <c r="N36">
         <v>2.2750661366047948</v>
       </c>
-      <c r="O33">
+      <c r="O36">
         <v>7.0555555555555562</v>
       </c>
-      <c r="P33">
+      <c r="P36">
         <v>3.3096380019125498</v>
       </c>
     </row>
@@ -1391,6 +1501,664 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
+  <dimension ref="A2:AF14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" t="s">
+        <v>49</v>
+      </c>
+      <c r="W2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>73</v>
+      </c>
+      <c r="C4">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>72</v>
+      </c>
+      <c r="G4">
+        <v>84</v>
+      </c>
+      <c r="H4">
+        <v>16</v>
+      </c>
+      <c r="I4">
+        <v>41</v>
+      </c>
+      <c r="J4">
+        <v>59</v>
+      </c>
+      <c r="L4">
+        <v>87</v>
+      </c>
+      <c r="M4">
+        <v>13</v>
+      </c>
+      <c r="N4">
+        <v>12</v>
+      </c>
+      <c r="O4">
+        <v>88</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>27.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>28.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>12.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q9)</f>
+        <v>27.25</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q9)</f>
+        <v>4.6124830622995248</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R9)</f>
+        <v>27.833333333333332</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R9)</f>
+        <v>2.9944392908634274</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S9)</f>
+        <v>10.416666666666666</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S9)</f>
+        <v>2.8533605917701106</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T9)</f>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T9)</f>
+        <v>2.3452078799117149</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>10.333333333333332</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD9)</f>
+        <v>11.416666666666664</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD9)</f>
+        <v>3.2158461820595017</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>67</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>83</v>
+      </c>
+      <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <v>35</v>
+      </c>
+      <c r="J5">
+        <v>65</v>
+      </c>
+      <c r="L5">
+        <v>95</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>13</v>
+      </c>
+      <c r="O5">
+        <v>87</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
+        <v>25</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
+        <v>25.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
+        <v>9</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
+        <v>19.833333333333332</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
+        <v>9</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD9" si="5">T5-AC5</f>
+        <v>10.833333333333332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>79</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>82</v>
+      </c>
+      <c r="G6">
+        <v>83</v>
+      </c>
+      <c r="H6">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>35</v>
+      </c>
+      <c r="J6">
+        <v>65</v>
+      </c>
+      <c r="L6">
+        <v>90</v>
+      </c>
+      <c r="M6">
+        <v>10</v>
+      </c>
+      <c r="N6">
+        <v>9</v>
+      </c>
+      <c r="O6">
+        <v>91</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>9.5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>18.333333333333332</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>8.8333333333333321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>64</v>
+      </c>
+      <c r="C7">
+        <v>36</v>
+      </c>
+      <c r="D7">
+        <v>28</v>
+      </c>
+      <c r="E7">
+        <v>72</v>
+      </c>
+      <c r="G7">
+        <v>76</v>
+      </c>
+      <c r="H7">
+        <v>24</v>
+      </c>
+      <c r="I7">
+        <v>43</v>
+      </c>
+      <c r="J7">
+        <v>57</v>
+      </c>
+      <c r="L7">
+        <v>97</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7">
+        <v>9</v>
+      </c>
+      <c r="O7">
+        <v>91</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>33.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>17.833333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>67</v>
+      </c>
+      <c r="C8">
+        <v>33</v>
+      </c>
+      <c r="D8">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>77</v>
+      </c>
+      <c r="G8">
+        <v>79</v>
+      </c>
+      <c r="H8">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>31</v>
+      </c>
+      <c r="J8">
+        <v>69</v>
+      </c>
+      <c r="L8">
+        <v>87</v>
+      </c>
+      <c r="M8">
+        <v>13</v>
+      </c>
+      <c r="N8">
+        <v>10</v>
+      </c>
+      <c r="O8">
+        <v>90</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>11.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>21.833333333333332</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>11.5</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>10.333333333333332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>66</v>
+      </c>
+      <c r="C9">
+        <v>34</v>
+      </c>
+      <c r="D9">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>71</v>
+      </c>
+      <c r="G9">
+        <v>79</v>
+      </c>
+      <c r="H9">
+        <v>21</v>
+      </c>
+      <c r="I9">
+        <v>34</v>
+      </c>
+      <c r="J9">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>85</v>
+      </c>
+      <c r="M9">
+        <v>15</v>
+      </c>
+      <c r="N9">
+        <v>13</v>
+      </c>
+      <c r="O9">
+        <v>87</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>31.5</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>27.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>24.333333333333332</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>10.333333333333332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>74</v>
+      </c>
+      <c r="C13">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>25</v>
+      </c>
+      <c r="E13">
+        <v>75</v>
+      </c>
+      <c r="G13">
+        <v>87</v>
+      </c>
+      <c r="H13">
+        <v>13</v>
+      </c>
+      <c r="I13">
+        <v>38</v>
+      </c>
+      <c r="J13">
+        <v>62</v>
+      </c>
+      <c r="L13">
+        <v>91</v>
+      </c>
+      <c r="M13">
+        <v>9</v>
+      </c>
+      <c r="N13">
+        <v>10</v>
+      </c>
+      <c r="O13">
+        <v>90</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" ref="Q10:Q14" si="6">AVERAGE(C13,D13)</f>
+        <v>25.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" ref="R10:R14" si="7">AVERAGE(H13,I13)</f>
+        <v>25.5</v>
+      </c>
+      <c r="S13">
+        <f t="shared" ref="S10:S14" si="8">AVERAGE(M13,N13)</f>
+        <v>9.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" ref="T10:T14" si="9">AVERAGE(Q13:S13)</f>
+        <v>20.166666666666668</v>
+      </c>
+      <c r="U13">
+        <f>AVERAGE(Q13:Q18)</f>
+        <v>27.25</v>
+      </c>
+      <c r="V13">
+        <f>_xlfn.STDEV.S(Q13:Q18)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="W13">
+        <f>AVERAGE(R13:R18)</f>
+        <v>25.75</v>
+      </c>
+      <c r="X13">
+        <f>_xlfn.STDEV.S(R13:R18)</f>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="Y13">
+        <f>AVERAGE(S13:S18)</f>
+        <v>9</v>
+      </c>
+      <c r="Z13">
+        <f>_xlfn.STDEV.S(S13:S18)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="AA13">
+        <f>AVERAGE(T13:T18)</f>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="AB13">
+        <f>_xlfn.STDEV.S(T13:T18)</f>
+        <v>0.70710678118654757</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" ref="AC10:AC14" si="10">MIN(Q13:S13)</f>
+        <v>9.5</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" ref="AD10:AD14" si="11">T13-AC13</f>
+        <v>10.666666666666668</v>
+      </c>
+      <c r="AE13">
+        <f>AVERAGE(AD13:AD18)</f>
+        <v>11.666666666666668</v>
+      </c>
+      <c r="AF13">
+        <f>_xlfn.STDEV.S(AD13:AD18)</f>
+        <v>1.4142135623730951</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>67</v>
+      </c>
+      <c r="C14">
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>75</v>
+      </c>
+      <c r="G14">
+        <v>79</v>
+      </c>
+      <c r="H14">
+        <v>21</v>
+      </c>
+      <c r="I14">
+        <v>31</v>
+      </c>
+      <c r="J14">
+        <v>69</v>
+      </c>
+      <c r="L14">
+        <v>94</v>
+      </c>
+      <c r="M14">
+        <v>6</v>
+      </c>
+      <c r="N14">
+        <v>11</v>
+      </c>
+      <c r="O14">
+        <v>89</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>29</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>8.5</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>21.166666666666668</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="10"/>
+        <v>8.5</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
   <dimension ref="A2:AF10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1938,7 +2706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AN99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4641,7 +5409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5373,7 +6141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6090,7 +6858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AR15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6967,7 +7735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AR10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7659,7 +8427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AR109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8136,27 +8904,27 @@
       </c>
       <c r="AI12">
         <f>AVERAGE(Q16:Q24)</f>
-        <v>28.5</v>
+        <v>28.9</v>
       </c>
       <c r="AJ12">
         <f>_xlfn.STDEV.S(Q16:Q24)</f>
-        <v>4.5825756949558398</v>
+        <v>4.1140004861448372</v>
       </c>
       <c r="AK12">
         <f>AVERAGE(R16:R24)</f>
-        <v>29.5</v>
+        <v>29</v>
       </c>
       <c r="AL12">
         <f>_xlfn.STDEV.S(R16:R24)</f>
-        <v>3.5</v>
+        <v>3.9528470752104741</v>
       </c>
       <c r="AM12">
         <f>AVERAGE(S16:S24)</f>
-        <v>10.166666666666666</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AN12">
         <f>_xlfn.STDEV.S(S16:S24)</f>
-        <v>1.4433756729740677</v>
+        <v>2.8853076092507024</v>
       </c>
       <c r="AO12">
         <v>20.537037037037035</v>
@@ -8308,11 +9076,11 @@
         <v>1.4433756729740677</v>
       </c>
       <c r="AC16">
-        <f>AVERAGE(T16:T24)</f>
+        <f>AVERAGE(T16:T18)</f>
         <v>22.722222222222225</v>
       </c>
       <c r="AD16">
-        <f>_xlfn.STDEV.S(T16:T24)</f>
+        <f>_xlfn.STDEV.S(T16:T18)</f>
         <v>2.3412563895228313</v>
       </c>
       <c r="AE16">
@@ -8320,7 +9088,7 @@
         <v>12.555555555555557</v>
       </c>
       <c r="AF16">
-        <f>_xlfn.STDEV.S(V16:V24)</f>
+        <f>_xlfn.STDEV.S(V16:V18)</f>
         <v>1.4174834246858978</v>
       </c>
     </row>
@@ -8448,6 +9216,175 @@
         <v>12</v>
       </c>
     </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>76</v>
+      </c>
+      <c r="C21">
+        <v>24</v>
+      </c>
+      <c r="D21">
+        <v>28</v>
+      </c>
+      <c r="E21">
+        <v>72</v>
+      </c>
+      <c r="G21">
+        <v>91</v>
+      </c>
+      <c r="H21">
+        <v>9</v>
+      </c>
+      <c r="I21">
+        <v>39</v>
+      </c>
+      <c r="J21">
+        <v>61</v>
+      </c>
+      <c r="L21">
+        <v>97</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>8</v>
+      </c>
+      <c r="O21">
+        <v>92</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" ref="Q19:Q22" si="6">AVERAGE(C21,D21)</f>
+        <v>26</v>
+      </c>
+      <c r="R21">
+        <f t="shared" ref="R19:R22" si="7">AVERAGE(H21:I21)</f>
+        <v>24</v>
+      </c>
+      <c r="S21">
+        <f t="shared" ref="S19:S22" si="8">AVERAGE(M21,N21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="T21">
+        <f t="shared" ref="T19:T22" si="9">AVERAGE(Q21:S21)</f>
+        <v>18.5</v>
+      </c>
+      <c r="U21">
+        <f t="shared" ref="U19:U22" si="10">MIN(Q21:S21)</f>
+        <v>5.5</v>
+      </c>
+      <c r="V21">
+        <f t="shared" ref="V19:V22" si="11">(T21-U21)</f>
+        <v>13</v>
+      </c>
+      <c r="W21">
+        <f>AVERAGE(Q21:Q23)</f>
+        <v>29.5</v>
+      </c>
+      <c r="X21">
+        <f>_xlfn.STDEV.S(Q21:Q23)</f>
+        <v>4.9497474683058327</v>
+      </c>
+      <c r="Y21">
+        <f>AVERAGE(R21:R23)</f>
+        <v>28.25</v>
+      </c>
+      <c r="Z21">
+        <f>_xlfn.STDEV.S(R21:R23)</f>
+        <v>6.0104076400856536</v>
+      </c>
+      <c r="AA21">
+        <f>AVERAGE(S21:S23)</f>
+        <v>9.25</v>
+      </c>
+      <c r="AB21">
+        <f>_xlfn.STDEV.S(S21:S23)</f>
+        <v>5.3033008588991066</v>
+      </c>
+      <c r="AC21">
+        <f>AVERAGE(T21:T23)</f>
+        <v>22.333333333333336</v>
+      </c>
+      <c r="AD21">
+        <f>_xlfn.STDEV.S(T21:T23)</f>
+        <v>5.4211519890968356</v>
+      </c>
+      <c r="AE21">
+        <f>AVERAGE(V21:V23)</f>
+        <v>13.083333333333334</v>
+      </c>
+      <c r="AF21">
+        <f>_xlfn.STDEV.S(V21:V23)</f>
+        <v>0.11785113019775875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>73</v>
+      </c>
+      <c r="C22">
+        <v>27</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
+      </c>
+      <c r="E22">
+        <v>61</v>
+      </c>
+      <c r="G22">
+        <v>76</v>
+      </c>
+      <c r="H22">
+        <v>24</v>
+      </c>
+      <c r="I22">
+        <v>41</v>
+      </c>
+      <c r="J22">
+        <v>59</v>
+      </c>
+      <c r="L22">
+        <v>92</v>
+      </c>
+      <c r="M22">
+        <v>8</v>
+      </c>
+      <c r="N22">
+        <v>18</v>
+      </c>
+      <c r="O22">
+        <v>82</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="6"/>
+        <v>33</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="7"/>
+        <v>32.5</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="9"/>
+        <v>26.166666666666668</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="11"/>
+        <v>13.166666666666668</v>
+      </c>
+    </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
@@ -9308,53 +10245,53 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q68" t="e">
-        <f t="shared" ref="Q68:Q109" si="6">AVERAGE(C68,D68)</f>
+        <f t="shared" ref="Q68:Q109" si="12">AVERAGE(C68,D68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R68" t="e">
-        <f t="shared" ref="R68:R109" si="7">AVERAGE(H68:I68)</f>
+        <f t="shared" ref="R68:R109" si="13">AVERAGE(H68:I68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S68" t="e">
-        <f t="shared" ref="S68:S109" si="8">AVERAGE(M68,N68)</f>
+        <f t="shared" ref="S68:S109" si="14">AVERAGE(M68,N68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T68" t="e">
-        <f t="shared" ref="T68:T109" si="9">AVERAGE(Q68:S68)</f>
+        <f t="shared" ref="T68:T109" si="15">AVERAGE(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U68" t="e">
-        <f t="shared" ref="U68:U109" si="10">MIN(Q68:S68)</f>
+        <f t="shared" ref="U68:U109" si="16">MIN(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" t="e">
-        <f t="shared" ref="V68:V109" si="11">(1/3)*(T68-U68)</f>
+        <f t="shared" ref="V68:V109" si="17">(1/3)*(T68-U68)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q69" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R69" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S69" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T69" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U69" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V69" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9370,27 +10307,27 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q73" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R73" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S73" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T73" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U73" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC73" t="e">
@@ -9412,53 +10349,53 @@
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q74" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R74" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S74" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T74" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V74" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q75" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R75" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S75" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T75" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U75" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V75" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9474,27 +10411,27 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q79" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R79" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S79" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T79" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U79" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC79" t="e">
@@ -9516,235 +10453,235 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q80" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R80" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S80" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T80" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U80" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V80" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q81" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R81" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S81" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T81" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U81" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V81" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q82" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R82" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S82" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T82" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U82" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V82" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q83" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R83" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S83" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T83" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U83" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V83" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q84" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R84" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S84" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T84" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U84" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V84" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q85" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R85" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S85" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T85" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U85" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q86" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R86" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S86" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T86" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U86" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V86" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q87" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R87" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S87" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T87" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U87" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V87" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q88" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R88" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S88" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T88" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V88" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9760,27 +10697,27 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q92" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R92" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S92" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T92" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U92" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V92" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC92" t="e">
@@ -9802,131 +10739,131 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q93" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R93" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S93" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T93" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U93" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V93" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q94" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R94" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S94" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T94" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U94" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V94" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q95" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R95" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S95" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T95" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U95" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V95" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q96" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R96" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S96" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T96" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U96" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V96" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q97" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R97" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S97" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T97" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V97" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -9942,27 +10879,27 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q101" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R101" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S101" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T101" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U101" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V101" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC101" t="e">
@@ -9984,209 +10921,209 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q102" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R102" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S102" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T102" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U102" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q103" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R103" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S103" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T103" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U103" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q104" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R104" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S104" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T104" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U104" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V104" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q105" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R105" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S105" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T105" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U105" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q106" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R106" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S106" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T106" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q107" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R107" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S107" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T107" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U107" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q108" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R108" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S108" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T108" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U108" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q109" t="e">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" t="e">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S109" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T109" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U109" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10195,7 +11132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10497,6 +11434,293 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6405F3E4-2BE7-409E-B00B-8F78502D7FC2}">
+  <dimension ref="B2:AF6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" t="s">
+        <v>49</v>
+      </c>
+      <c r="W2" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>76</v>
+      </c>
+      <c r="C4">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>35</v>
+      </c>
+      <c r="E4">
+        <v>65</v>
+      </c>
+      <c r="G4">
+        <v>73</v>
+      </c>
+      <c r="H4">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>42</v>
+      </c>
+      <c r="J4">
+        <v>58</v>
+      </c>
+      <c r="L4">
+        <v>94</v>
+      </c>
+      <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="N4">
+        <v>13</v>
+      </c>
+      <c r="O4">
+        <v>87</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>29.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>34.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>9.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>24.5</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q7)</f>
+        <v>30.666666666666668</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q7)</f>
+        <v>1.0408329997330663</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R7)</f>
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R7)</f>
+        <v>4.7696960070847281</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S7)</f>
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S7)</f>
+        <v>1.8929694486000899</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T7)</f>
+        <v>23.111111111111111</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T7)</f>
+        <v>1.9883922409081429</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>9.5</v>
+      </c>
+      <c r="AD4">
+        <f>(T4-AC4)</f>
+        <v>15</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD7)</f>
+        <v>14.444444444444443</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD7)</f>
+        <v>0.5091750772173157</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>76</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>38</v>
+      </c>
+      <c r="E5">
+        <v>62</v>
+      </c>
+      <c r="G5">
+        <v>92</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <v>42</v>
+      </c>
+      <c r="J5">
+        <v>58</v>
+      </c>
+      <c r="L5">
+        <v>95</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <v>92</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q6" si="0">AVERAGE(C5,D5)</f>
+        <v>31</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R6" si="1">AVERAGE(H5,I5)</f>
+        <v>25</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S6" si="2">AVERAGE(M5,N5)</f>
+        <v>6.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T6" si="3">AVERAGE(Q5:S5)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC6" si="4">MIN(Q5:S5)</f>
+        <v>6.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD6" si="5">(T5-AC5)</f>
+        <v>14.333333333333332</v>
+      </c>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>27</v>
+      </c>
+      <c r="D6">
+        <v>36</v>
+      </c>
+      <c r="E6">
+        <v>64</v>
+      </c>
+      <c r="G6">
+        <v>86</v>
+      </c>
+      <c r="H6">
+        <v>14</v>
+      </c>
+      <c r="I6">
+        <v>47</v>
+      </c>
+      <c r="J6">
+        <v>53</v>
+      </c>
+      <c r="L6">
+        <v>95</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <v>15</v>
+      </c>
+      <c r="O6">
+        <v>85</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>31.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>30.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
   <dimension ref="A2:AF15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10899,19 +12123,19 @@
         <v>84</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q8:Q15" si="6">AVERAGE(C12,D12)</f>
+        <f t="shared" ref="Q12:Q15" si="6">AVERAGE(C12,D12)</f>
         <v>33.5</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R8:R15" si="7">AVERAGE(H12,I12)</f>
+        <f t="shared" ref="R12:R15" si="7">AVERAGE(H12,I12)</f>
         <v>31.5</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S8:S15" si="8">AVERAGE(M12,N12)</f>
+        <f t="shared" ref="S12:S15" si="8">AVERAGE(M12,N12)</f>
         <v>10.5</v>
       </c>
       <c r="T12">
-        <f t="shared" ref="T8:T15" si="9">AVERAGE(Q12:S12)</f>
+        <f t="shared" ref="T12:T15" si="9">AVERAGE(Q12:S12)</f>
         <v>25.166666666666668</v>
       </c>
       <c r="U12">
@@ -10947,11 +12171,11 @@
         <v>2.1125725935368393</v>
       </c>
       <c r="AC12">
-        <f t="shared" ref="AC8:AC15" si="10">MIN(Q12:S12)</f>
+        <f t="shared" ref="AC12:AC15" si="10">MIN(Q12:S12)</f>
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <f t="shared" ref="AD8:AD15" si="11">(T12-AC12)</f>
+        <f t="shared" ref="AD12:AD15" si="11">(T12-AC12)</f>
         <v>14.666666666666668</v>
       </c>
       <c r="AE12">
@@ -11154,7 +12378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11313,16 +12537,16 @@
         <v>9.5</v>
       </c>
       <c r="AD4">
-        <f>(1/3)*(T4-AC4)</f>
-        <v>4.3888888888888893</v>
+        <f>(T4-AC4)</f>
+        <v>13.166666666666668</v>
       </c>
       <c r="AE4">
         <f>AVERAGE(AD4,AD5:AD6)</f>
-        <v>3.5555555555555558</v>
+        <v>10.666666666666666</v>
       </c>
       <c r="AF4">
         <f>_xlfn.STDEV.S(AD4,AD5:AD6)</f>
-        <v>0.80699105812966365</v>
+        <v>2.4209731743889984</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
@@ -11383,8 +12607,8 @@
         <v>6.5</v>
       </c>
       <c r="AD5">
-        <f>(1/3)*(T5-AC5)</f>
-        <v>2.7777777777777777</v>
+        <f t="shared" ref="AD5:AD6" si="0">(T5-AC5)</f>
+        <v>8.3333333333333339</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
@@ -11445,8 +12669,8 @@
         <v>5</v>
       </c>
       <c r="AD6">
-        <f>(1/3)*(T6-AC6)</f>
-        <v>3.5</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
     </row>
   </sheetData>
@@ -11454,7 +12678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
   <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11797,19 +13021,19 @@
         <v>85</v>
       </c>
       <c r="Q12">
-        <f t="shared" ref="Q7:Q14" si="6">AVERAGE(C12:D12)</f>
+        <f t="shared" ref="Q12:Q14" si="6">AVERAGE(C12:D12)</f>
         <v>20</v>
       </c>
       <c r="R12">
-        <f t="shared" ref="R7:R14" si="7">AVERAGE(H12:I12)</f>
+        <f t="shared" ref="R12:R14" si="7">AVERAGE(H12:I12)</f>
         <v>16.5</v>
       </c>
       <c r="S12">
-        <f t="shared" ref="S7:S14" si="8">AVERAGE(M12:N12)</f>
+        <f t="shared" ref="S12:S14" si="8">AVERAGE(M12:N12)</f>
         <v>12</v>
       </c>
       <c r="T12">
-        <f t="shared" ref="T7:T14" si="9">AVERAGE(Q12:S12)</f>
+        <f t="shared" ref="T12:T14" si="9">AVERAGE(Q12:S12)</f>
         <v>16.166666666666668</v>
       </c>
       <c r="U12">
@@ -11845,11 +13069,11 @@
         <v>2.2750661366047948</v>
       </c>
       <c r="AC12">
-        <f t="shared" ref="AC7:AC14" si="10">MIN(Q12:S12)</f>
+        <f t="shared" ref="AC12:AC14" si="10">MIN(Q12:S12)</f>
         <v>12</v>
       </c>
       <c r="AD12">
-        <f t="shared" ref="AD7:AD14" si="11">T12-AC12</f>
+        <f t="shared" ref="AD12:AD14" si="11">T12-AC12</f>
         <v>4.1666666666666679</v>
       </c>
       <c r="AE12">
@@ -11990,7 +13214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
   <dimension ref="A2:AF26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12807,19 +14031,19 @@
         <v>94</v>
       </c>
       <c r="Q21">
-        <f t="shared" ref="Q15:Q26" si="12">AVERAGE(C21,D21)</f>
+        <f t="shared" ref="Q21:Q26" si="12">AVERAGE(C21,D21)</f>
         <v>27</v>
       </c>
       <c r="R21">
-        <f t="shared" ref="R15:R26" si="13">AVERAGE(H21,I21)</f>
+        <f t="shared" ref="R21:R26" si="13">AVERAGE(H21,I21)</f>
         <v>31</v>
       </c>
       <c r="S21">
-        <f t="shared" ref="S15:S26" si="14">AVERAGE(M21,N21)</f>
+        <f t="shared" ref="S21:S26" si="14">AVERAGE(M21,N21)</f>
         <v>10</v>
       </c>
       <c r="T21">
-        <f t="shared" ref="T15:T26" si="15">AVERAGE(Q21:S21)</f>
+        <f t="shared" ref="T21:T26" si="15">AVERAGE(Q21:S21)</f>
         <v>22.666666666666668</v>
       </c>
       <c r="U21">
@@ -12855,11 +14079,11 @@
         <v>1.2560962454277844</v>
       </c>
       <c r="AC21">
-        <f t="shared" ref="AC15:AC26" si="16">MIN(Q21:S21)</f>
+        <f t="shared" ref="AC21:AC26" si="16">MIN(Q21:S21)</f>
         <v>10</v>
       </c>
       <c r="AD21">
-        <f t="shared" ref="AD15:AD26" si="17">(T21-AC21)</f>
+        <f t="shared" ref="AD21:AD26" si="17">(T21-AC21)</f>
         <v>12.666666666666668</v>
       </c>
       <c r="AE21">
@@ -13186,7 +14410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13349,7 +14573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13652,7 +14876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14139,493 +15363,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S2" t="s">
-        <v>14</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V2" t="s">
-        <v>49</v>
-      </c>
-      <c r="W2" t="s">
-        <v>57</v>
-      </c>
-      <c r="X2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
-        <v>67</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>73</v>
-      </c>
-      <c r="C4">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>28</v>
-      </c>
-      <c r="E4">
-        <v>72</v>
-      </c>
-      <c r="G4">
-        <v>84</v>
-      </c>
-      <c r="H4">
-        <v>16</v>
-      </c>
-      <c r="I4">
-        <v>41</v>
-      </c>
-      <c r="J4">
-        <v>59</v>
-      </c>
-      <c r="L4">
-        <v>87</v>
-      </c>
-      <c r="M4">
-        <v>13</v>
-      </c>
-      <c r="N4">
-        <v>12</v>
-      </c>
-      <c r="O4">
-        <v>88</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>27.5</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>28.5</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>12.5</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>22.833333333333332</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q9)</f>
-        <v>27.25</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q9)</f>
-        <v>4.6124830622995248</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R9)</f>
-        <v>27.833333333333332</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R9)</f>
-        <v>2.9944392908634274</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S9)</f>
-        <v>10.416666666666666</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S9)</f>
-        <v>2.8533605917701106</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T9)</f>
-        <v>21.833333333333332</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T9)</f>
-        <v>2.3452078799117149</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>12.5</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>10.333333333333332</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD9)</f>
-        <v>11.416666666666664</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD9)</f>
-        <v>3.2158461820595017</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>67</v>
-      </c>
-      <c r="C5">
-        <v>33</v>
-      </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>83</v>
-      </c>
-      <c r="G5">
-        <v>84</v>
-      </c>
-      <c r="H5">
-        <v>16</v>
-      </c>
-      <c r="I5">
-        <v>35</v>
-      </c>
-      <c r="J5">
-        <v>65</v>
-      </c>
-      <c r="L5">
-        <v>95</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-      <c r="N5">
-        <v>13</v>
-      </c>
-      <c r="O5">
-        <v>87</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q9" si="0">AVERAGE(C5,D5)</f>
-        <v>25</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R9" si="1">AVERAGE(H5,I5)</f>
-        <v>25.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S9" si="2">AVERAGE(M5,N5)</f>
-        <v>9</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T9" si="3">AVERAGE(Q5:S5)</f>
-        <v>19.833333333333332</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC9" si="4">MIN(Q5:S5)</f>
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD9" si="5">T5-AC5</f>
-        <v>10.833333333333332</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>79</v>
-      </c>
-      <c r="C6">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>82</v>
-      </c>
-      <c r="G6">
-        <v>83</v>
-      </c>
-      <c r="H6">
-        <v>17</v>
-      </c>
-      <c r="I6">
-        <v>35</v>
-      </c>
-      <c r="J6">
-        <v>65</v>
-      </c>
-      <c r="L6">
-        <v>90</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-      <c r="N6">
-        <v>9</v>
-      </c>
-      <c r="O6">
-        <v>91</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>9.5</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>18.333333333333332</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>8.8333333333333321</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>64</v>
-      </c>
-      <c r="C7">
-        <v>36</v>
-      </c>
-      <c r="D7">
-        <v>28</v>
-      </c>
-      <c r="E7">
-        <v>72</v>
-      </c>
-      <c r="G7">
-        <v>76</v>
-      </c>
-      <c r="H7">
-        <v>24</v>
-      </c>
-      <c r="I7">
-        <v>43</v>
-      </c>
-      <c r="J7">
-        <v>57</v>
-      </c>
-      <c r="L7">
-        <v>97</v>
-      </c>
-      <c r="M7">
-        <v>3</v>
-      </c>
-      <c r="N7">
-        <v>9</v>
-      </c>
-      <c r="O7">
-        <v>91</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>33.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>23.833333333333332</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>17.833333333333332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>67</v>
-      </c>
-      <c r="C8">
-        <v>33</v>
-      </c>
-      <c r="D8">
-        <v>23</v>
-      </c>
-      <c r="E8">
-        <v>77</v>
-      </c>
-      <c r="G8">
-        <v>79</v>
-      </c>
-      <c r="H8">
-        <v>21</v>
-      </c>
-      <c r="I8">
-        <v>31</v>
-      </c>
-      <c r="J8">
-        <v>69</v>
-      </c>
-      <c r="L8">
-        <v>87</v>
-      </c>
-      <c r="M8">
-        <v>13</v>
-      </c>
-      <c r="N8">
-        <v>10</v>
-      </c>
-      <c r="O8">
-        <v>90</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>11.5</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>21.833333333333332</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>11.5</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>10.333333333333332</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>66</v>
-      </c>
-      <c r="C9">
-        <v>34</v>
-      </c>
-      <c r="D9">
-        <v>29</v>
-      </c>
-      <c r="E9">
-        <v>71</v>
-      </c>
-      <c r="G9">
-        <v>79</v>
-      </c>
-      <c r="H9">
-        <v>21</v>
-      </c>
-      <c r="I9">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>66</v>
-      </c>
-      <c r="L9">
-        <v>85</v>
-      </c>
-      <c r="M9">
-        <v>15</v>
-      </c>
-      <c r="N9">
-        <v>13</v>
-      </c>
-      <c r="O9">
-        <v>87</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>31.5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>27.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>24.333333333333332</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>14</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>10.333333333333332</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/DataAnalysis/LT/0.05/Results.xlsx
+++ b/DataAnalysis/LT/0.05/Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\LT\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FAD4F67-C8E8-49C7-B619-A51DC72E928D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113FA43B-BBD4-47E3-9C49-BF3E5A6E1853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="77">
   <si>
     <t>Dati originali</t>
   </si>
@@ -681,8 +681,35 @@
       <c r="P3">
         <v>0.53575837561071948</v>
       </c>
-      <c r="R3" t="s">
-        <v>76</v>
+      <c r="R3">
+        <v>30.666666666666668</v>
+      </c>
+      <c r="S3">
+        <v>5.0579969684978323</v>
+      </c>
+      <c r="T3">
+        <v>30.666666666666668</v>
+      </c>
+      <c r="U3">
+        <v>4.5092497528228863</v>
+      </c>
+      <c r="V3">
+        <v>10.833333333333334</v>
+      </c>
+      <c r="W3">
+        <v>2.8431203515386652</v>
+      </c>
+      <c r="X3">
+        <v>24.055555555555557</v>
+      </c>
+      <c r="Y3">
+        <v>2.6943012562182544</v>
+      </c>
+      <c r="Z3">
+        <v>13.222222222222223</v>
+      </c>
+      <c r="AA3">
+        <v>4.3853713048590777</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
@@ -723,34 +750,34 @@
         <v>1.4174834246858978</v>
       </c>
       <c r="R4">
-        <v>29.5</v>
+        <v>31.7</v>
       </c>
       <c r="S4">
-        <v>4.9497474683058327</v>
+        <v>3.8013155617496484</v>
       </c>
       <c r="T4">
-        <v>28.25</v>
+        <v>30.7</v>
       </c>
       <c r="U4">
-        <v>6.0104076400856536</v>
+        <v>4.644889664997442</v>
       </c>
       <c r="V4">
-        <v>9.25</v>
+        <v>11.1</v>
       </c>
       <c r="W4">
-        <v>5.3033008588991066</v>
+        <v>3.3429029300893576</v>
       </c>
       <c r="X4">
-        <v>22.333333333333336</v>
+        <v>24.5</v>
       </c>
       <c r="Y4">
-        <v>5.4211519890968356</v>
+        <v>3.4176827757349777</v>
       </c>
       <c r="Z4">
-        <v>13.083333333333334</v>
+        <v>13.4</v>
       </c>
       <c r="AA4">
-        <v>0.11785113019775875</v>
+        <v>0.77817450199524985</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
@@ -1079,6 +1106,36 @@
       <c r="P20">
         <v>3.5207247329921398</v>
       </c>
+      <c r="R20">
+        <v>37.666666666666664</v>
+      </c>
+      <c r="S20">
+        <v>1.4433756729740643</v>
+      </c>
+      <c r="T20">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="U20">
+        <v>4.5092497528228863</v>
+      </c>
+      <c r="V20">
+        <v>11.166666666666666</v>
+      </c>
+      <c r="W20">
+        <v>2.7537852736430528</v>
+      </c>
+      <c r="X20">
+        <v>27.388888888888886</v>
+      </c>
+      <c r="Y20">
+        <v>2.1430335024428788</v>
+      </c>
+      <c r="Z20">
+        <v>16.222222222222221</v>
+      </c>
+      <c r="AA20">
+        <v>2.6369876191790693</v>
+      </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
@@ -1121,34 +1178,34 @@
         <v>76</v>
       </c>
       <c r="R21">
-        <v>27.25</v>
+        <v>26.625</v>
       </c>
       <c r="S21">
-        <v>2.4748737341529163</v>
+        <v>3.6371921404658658</v>
       </c>
       <c r="T21">
-        <v>25.75</v>
+        <v>27.625</v>
       </c>
       <c r="U21">
-        <v>0.35355339059327379</v>
+        <v>2.2126530078919591</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W21">
-        <v>0.70710678118654757</v>
+        <v>2.1602468994692869</v>
       </c>
       <c r="X21">
-        <v>20.6666666666667</v>
+        <v>20.916666666666668</v>
       </c>
       <c r="Y21">
-        <v>0.70710678118654757</v>
+        <v>1.707825127659933</v>
       </c>
       <c r="Z21">
-        <v>11.666666666666668</v>
+        <v>12.416666666666668</v>
       </c>
       <c r="AA21">
-        <v>1.4142135623730951</v>
+        <v>1.2583057392117916</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
@@ -1339,6 +1396,36 @@
       </c>
       <c r="P30">
         <v>1.9254629073050034</v>
+      </c>
+      <c r="R30">
+        <v>22.333333333333332</v>
+      </c>
+      <c r="S30">
+        <v>3.2145502536643242</v>
+      </c>
+      <c r="T30">
+        <v>21</v>
+      </c>
+      <c r="U30">
+        <v>4</v>
+      </c>
+      <c r="V30">
+        <v>10.333333333333334</v>
+      </c>
+      <c r="W30">
+        <v>3.2532035493238571</v>
+      </c>
+      <c r="X30">
+        <v>17.888888888888889</v>
+      </c>
+      <c r="Y30">
+        <v>1.0584754935143132</v>
+      </c>
+      <c r="Z30">
+        <v>7.5555555555555562</v>
+      </c>
+      <c r="AA30">
+        <v>2.364866294865863</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
@@ -1502,7 +1589,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
-  <dimension ref="A2:AF14"/>
+  <dimension ref="A2:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -2027,68 +2114,68 @@
         <v>90</v>
       </c>
       <c r="Q13">
-        <f t="shared" ref="Q10:Q14" si="6">AVERAGE(C13,D13)</f>
+        <f t="shared" ref="Q13:Q14" si="6">AVERAGE(C13,D13)</f>
         <v>25.5</v>
       </c>
       <c r="R13">
-        <f t="shared" ref="R10:R14" si="7">AVERAGE(H13,I13)</f>
+        <f t="shared" ref="R13:R14" si="7">AVERAGE(H13,I13)</f>
         <v>25.5</v>
       </c>
       <c r="S13">
-        <f t="shared" ref="S10:S14" si="8">AVERAGE(M13,N13)</f>
+        <f t="shared" ref="S13:S14" si="8">AVERAGE(M13,N13)</f>
         <v>9.5</v>
       </c>
       <c r="T13">
-        <f t="shared" ref="T10:T14" si="9">AVERAGE(Q13:S13)</f>
+        <f t="shared" ref="T13:T14" si="9">AVERAGE(Q13:S13)</f>
         <v>20.166666666666668</v>
       </c>
       <c r="U13">
         <f>AVERAGE(Q13:Q18)</f>
-        <v>27.25</v>
+        <v>26.625</v>
       </c>
       <c r="V13">
         <f>_xlfn.STDEV.S(Q13:Q18)</f>
-        <v>2.4748737341529163</v>
+        <v>3.6371921404658658</v>
       </c>
       <c r="W13">
         <f>AVERAGE(R13:R18)</f>
-        <v>25.75</v>
+        <v>27.625</v>
       </c>
       <c r="X13">
         <f>_xlfn.STDEV.S(R13:R18)</f>
-        <v>0.35355339059327379</v>
+        <v>2.2126530078919591</v>
       </c>
       <c r="Y13">
         <f>AVERAGE(S13:S18)</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Z13">
         <f>_xlfn.STDEV.S(S13:S18)</f>
-        <v>0.70710678118654757</v>
+        <v>2.1602468994692869</v>
       </c>
       <c r="AA13">
         <f>AVERAGE(T13:T18)</f>
-        <v>20.666666666666668</v>
+        <v>20.916666666666668</v>
       </c>
       <c r="AB13">
         <f>_xlfn.STDEV.S(T13:T18)</f>
-        <v>0.70710678118654757</v>
+        <v>1.707825127659933</v>
       </c>
       <c r="AC13">
-        <f t="shared" ref="AC10:AC14" si="10">MIN(Q13:S13)</f>
+        <f t="shared" ref="AC13:AC14" si="10">MIN(Q13:S13)</f>
         <v>9.5</v>
       </c>
       <c r="AD13">
-        <f t="shared" ref="AD10:AD14" si="11">T13-AC13</f>
+        <f t="shared" ref="AD13:AD14" si="11">T13-AC13</f>
         <v>10.666666666666668</v>
       </c>
       <c r="AE13">
         <f>AVERAGE(AD13:AD18)</f>
-        <v>11.666666666666668</v>
+        <v>12.416666666666668</v>
       </c>
       <c r="AF13">
         <f>_xlfn.STDEV.S(AD13:AD18)</f>
-        <v>1.4142135623730951</v>
+        <v>1.2583057392117916</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.3">
@@ -2150,6 +2237,130 @@
       </c>
       <c r="AD14">
         <f t="shared" si="11"/>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>84</v>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>28</v>
+      </c>
+      <c r="E15">
+        <v>72</v>
+      </c>
+      <c r="G15">
+        <v>84</v>
+      </c>
+      <c r="H15">
+        <v>16</v>
+      </c>
+      <c r="I15">
+        <v>44</v>
+      </c>
+      <c r="J15">
+        <v>56</v>
+      </c>
+      <c r="L15">
+        <v>96</v>
+      </c>
+      <c r="M15">
+        <v>4</v>
+      </c>
+      <c r="N15">
+        <v>7</v>
+      </c>
+      <c r="O15">
+        <v>93</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" ref="Q15:Q16" si="12">AVERAGE(C15,D15)</f>
+        <v>22</v>
+      </c>
+      <c r="R15">
+        <f t="shared" ref="R15:R16" si="13">AVERAGE(H15,I15)</f>
+        <v>30</v>
+      </c>
+      <c r="S15">
+        <f t="shared" ref="S15:S16" si="14">AVERAGE(M15,N15)</f>
+        <v>5.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" ref="T15:T16" si="15">AVERAGE(Q15:S15)</f>
+        <v>19.166666666666668</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" ref="AC15:AC16" si="16">MIN(Q15:S15)</f>
+        <v>5.5</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" ref="AD15:AD16" si="17">T15-AC15</f>
+        <v>13.666666666666668</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>63</v>
+      </c>
+      <c r="C16">
+        <v>37</v>
+      </c>
+      <c r="D16">
+        <v>23</v>
+      </c>
+      <c r="E16">
+        <v>77</v>
+      </c>
+      <c r="G16">
+        <v>81</v>
+      </c>
+      <c r="H16">
+        <v>19</v>
+      </c>
+      <c r="I16">
+        <v>39</v>
+      </c>
+      <c r="J16">
+        <v>61</v>
+      </c>
+      <c r="L16">
+        <v>93</v>
+      </c>
+      <c r="M16">
+        <v>7</v>
+      </c>
+      <c r="N16">
+        <v>14</v>
+      </c>
+      <c r="O16">
+        <v>86</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="14"/>
+        <v>10.5</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="15"/>
+        <v>23.166666666666668</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="16"/>
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="17"/>
         <v>12.666666666666668</v>
       </c>
     </row>
@@ -2160,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
-  <dimension ref="A2:AF10"/>
+  <dimension ref="A2:AF16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -2699,6 +2910,232 @@
       <c r="AD10">
         <f t="shared" si="5"/>
         <v>14.666666666666668</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>55</v>
+      </c>
+      <c r="C14">
+        <v>45</v>
+      </c>
+      <c r="D14">
+        <v>32</v>
+      </c>
+      <c r="E14">
+        <v>68</v>
+      </c>
+      <c r="G14">
+        <v>54</v>
+      </c>
+      <c r="H14">
+        <v>46</v>
+      </c>
+      <c r="I14">
+        <v>20</v>
+      </c>
+      <c r="J14">
+        <v>80</v>
+      </c>
+      <c r="L14">
+        <v>91</v>
+      </c>
+      <c r="M14">
+        <v>9</v>
+      </c>
+      <c r="N14">
+        <v>7</v>
+      </c>
+      <c r="O14">
+        <v>93</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" ref="Q11:Q16" si="6">AVERAGE(C14,D14)</f>
+        <v>38.5</v>
+      </c>
+      <c r="R14">
+        <f t="shared" ref="R11:R16" si="7">AVERAGE(H14,I14)</f>
+        <v>33</v>
+      </c>
+      <c r="S14">
+        <f t="shared" ref="S11:S16" si="8">AVERAGE(M14,N14)</f>
+        <v>8</v>
+      </c>
+      <c r="T14">
+        <f t="shared" ref="T11:T16" si="9">AVERAGE(Q14:S14)</f>
+        <v>26.5</v>
+      </c>
+      <c r="U14">
+        <f>AVERAGE(Q14:Q20)</f>
+        <v>37.666666666666664</v>
+      </c>
+      <c r="V14">
+        <f>_xlfn.STDEV.S(Q14:Q20)</f>
+        <v>1.4433756729740643</v>
+      </c>
+      <c r="W14">
+        <f>AVERAGE(R14:R20)</f>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="X14">
+        <f>_xlfn.STDEV.S(R14:R20)</f>
+        <v>4.5092497528228863</v>
+      </c>
+      <c r="Y14">
+        <f>AVERAGE(S14:S20)</f>
+        <v>11.166666666666666</v>
+      </c>
+      <c r="Z14">
+        <f>_xlfn.STDEV.S(S14:S20)</f>
+        <v>2.7537852736430528</v>
+      </c>
+      <c r="AA14">
+        <f>AVERAGE(T14:T20)</f>
+        <v>27.388888888888886</v>
+      </c>
+      <c r="AB14">
+        <f>_xlfn.STDEV.S(T14:T20)</f>
+        <v>2.1430335024428788</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" ref="AC11:AC16" si="10">MIN(Q14:S14)</f>
+        <v>8</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" ref="AD11:AD16" si="11">T14-AC14</f>
+        <v>18.5</v>
+      </c>
+      <c r="AE14">
+        <f>AVERAGE(AD14:AD20)</f>
+        <v>16.222222222222221</v>
+      </c>
+      <c r="AF14">
+        <f>_xlfn.STDEV.S(AD14:AD20)</f>
+        <v>2.6369876191790693</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>54</v>
+      </c>
+      <c r="C15">
+        <v>46</v>
+      </c>
+      <c r="D15">
+        <v>26</v>
+      </c>
+      <c r="E15">
+        <v>74</v>
+      </c>
+      <c r="G15">
+        <v>71</v>
+      </c>
+      <c r="H15">
+        <v>29</v>
+      </c>
+      <c r="I15">
+        <v>29</v>
+      </c>
+      <c r="J15">
+        <v>71</v>
+      </c>
+      <c r="L15">
+        <v>88</v>
+      </c>
+      <c r="M15">
+        <v>12</v>
+      </c>
+      <c r="N15">
+        <v>13</v>
+      </c>
+      <c r="O15">
+        <v>87</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="6"/>
+        <v>36</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="7"/>
+        <v>29</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="8"/>
+        <v>12.5</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="9"/>
+        <v>25.833333333333332</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="11"/>
+        <v>13.333333333333332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>43</v>
+      </c>
+      <c r="C16">
+        <v>57</v>
+      </c>
+      <c r="D16">
+        <v>20</v>
+      </c>
+      <c r="E16">
+        <v>80</v>
+      </c>
+      <c r="G16">
+        <v>48</v>
+      </c>
+      <c r="H16">
+        <v>52</v>
+      </c>
+      <c r="I16">
+        <v>24</v>
+      </c>
+      <c r="J16">
+        <v>76</v>
+      </c>
+      <c r="L16">
+        <v>90</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16">
+        <v>16</v>
+      </c>
+      <c r="O16">
+        <v>84</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="6"/>
+        <v>38.5</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="7"/>
+        <v>38</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="8"/>
+        <v>13</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="9"/>
+        <v>29.833333333333332</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="11"/>
+        <v>16.833333333333332</v>
       </c>
     </row>
   </sheetData>
@@ -8904,27 +9341,27 @@
       </c>
       <c r="AI12">
         <f>AVERAGE(Q16:Q24)</f>
-        <v>28.9</v>
+        <v>30.285714285714285</v>
       </c>
       <c r="AJ12">
         <f>_xlfn.STDEV.S(Q16:Q24)</f>
-        <v>4.1140004861448372</v>
+        <v>4.4050836433332261</v>
       </c>
       <c r="AK12">
         <f>AVERAGE(R16:R24)</f>
-        <v>29</v>
+        <v>29.5</v>
       </c>
       <c r="AL12">
         <f>_xlfn.STDEV.S(R16:R24)</f>
-        <v>3.9528470752104741</v>
+        <v>3.6968455021364721</v>
       </c>
       <c r="AM12">
         <f>AVERAGE(S16:S24)</f>
-        <v>9.8000000000000007</v>
+        <v>10.428571428571429</v>
       </c>
       <c r="AN12">
         <f>_xlfn.STDEV.S(S16:S24)</f>
-        <v>2.8853076092507024</v>
+        <v>2.7299049346783022</v>
       </c>
       <c r="AO12">
         <v>20.537037037037035</v>
@@ -9259,68 +9696,68 @@
         <v>92</v>
       </c>
       <c r="Q21">
-        <f t="shared" ref="Q19:Q22" si="6">AVERAGE(C21,D21)</f>
+        <f t="shared" ref="Q21:Q22" si="6">AVERAGE(C21,D21)</f>
         <v>26</v>
       </c>
       <c r="R21">
-        <f t="shared" ref="R19:R22" si="7">AVERAGE(H21:I21)</f>
+        <f t="shared" ref="R21:R22" si="7">AVERAGE(H21:I21)</f>
         <v>24</v>
       </c>
       <c r="S21">
-        <f t="shared" ref="S19:S22" si="8">AVERAGE(M21,N21)</f>
+        <f t="shared" ref="S21:S22" si="8">AVERAGE(M21,N21)</f>
         <v>5.5</v>
       </c>
       <c r="T21">
-        <f t="shared" ref="T19:T22" si="9">AVERAGE(Q21:S21)</f>
+        <f t="shared" ref="T21:T22" si="9">AVERAGE(Q21:S21)</f>
         <v>18.5</v>
       </c>
       <c r="U21">
-        <f t="shared" ref="U19:U22" si="10">MIN(Q21:S21)</f>
+        <f t="shared" ref="U21:U22" si="10">MIN(Q21:S21)</f>
         <v>5.5</v>
       </c>
       <c r="V21">
-        <f t="shared" ref="V19:V22" si="11">(T21-U21)</f>
+        <f t="shared" ref="V21:V22" si="11">(T21-U21)</f>
         <v>13</v>
       </c>
       <c r="W21">
-        <f>AVERAGE(Q21:Q23)</f>
-        <v>29.5</v>
+        <f>AVERAGE(Q21:Q25)</f>
+        <v>31.7</v>
       </c>
       <c r="X21">
-        <f>_xlfn.STDEV.S(Q21:Q23)</f>
-        <v>4.9497474683058327</v>
+        <f>_xlfn.STDEV.S(Q21:Q25)</f>
+        <v>3.8013155617496484</v>
       </c>
       <c r="Y21">
-        <f>AVERAGE(R21:R23)</f>
-        <v>28.25</v>
+        <f>AVERAGE(R21:R25)</f>
+        <v>30.7</v>
       </c>
       <c r="Z21">
-        <f>_xlfn.STDEV.S(R21:R23)</f>
-        <v>6.0104076400856536</v>
+        <f>_xlfn.STDEV.S(R21:R25)</f>
+        <v>4.644889664997442</v>
       </c>
       <c r="AA21">
-        <f>AVERAGE(S21:S23)</f>
-        <v>9.25</v>
+        <f>AVERAGE(S21:S25)</f>
+        <v>11.1</v>
       </c>
       <c r="AB21">
-        <f>_xlfn.STDEV.S(S21:S23)</f>
-        <v>5.3033008588991066</v>
+        <f>_xlfn.STDEV.S(S21:S25)</f>
+        <v>3.3429029300893576</v>
       </c>
       <c r="AC21">
-        <f>AVERAGE(T21:T23)</f>
-        <v>22.333333333333336</v>
+        <f>AVERAGE(T21:T25)</f>
+        <v>24.5</v>
       </c>
       <c r="AD21">
-        <f>_xlfn.STDEV.S(T21:T23)</f>
-        <v>5.4211519890968356</v>
+        <f>_xlfn.STDEV.S(T21:T25)</f>
+        <v>3.4176827757349777</v>
       </c>
       <c r="AE21">
-        <f>AVERAGE(V21:V23)</f>
-        <v>13.083333333333334</v>
+        <f>AVERAGE(V21:V25)</f>
+        <v>13.4</v>
       </c>
       <c r="AF21">
-        <f>_xlfn.STDEV.S(V21:V23)</f>
-        <v>0.11785113019775875</v>
+        <f>_xlfn.STDEV.S(V21:V25)</f>
+        <v>0.77817450199524985</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.3">
@@ -9385,6 +9822,192 @@
         <v>13.166666666666668</v>
       </c>
     </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>57</v>
+      </c>
+      <c r="C23">
+        <v>43</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>70</v>
+      </c>
+      <c r="G23">
+        <v>79</v>
+      </c>
+      <c r="H23">
+        <v>21</v>
+      </c>
+      <c r="I23">
+        <v>35</v>
+      </c>
+      <c r="J23">
+        <v>65</v>
+      </c>
+      <c r="L23">
+        <v>94</v>
+      </c>
+      <c r="M23">
+        <v>6</v>
+      </c>
+      <c r="N23">
+        <v>21</v>
+      </c>
+      <c r="O23">
+        <v>79</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" ref="Q23:Q25" si="12">AVERAGE(C23,D23)</f>
+        <v>36.5</v>
+      </c>
+      <c r="R23">
+        <f t="shared" ref="R23:R25" si="13">AVERAGE(H23:I23)</f>
+        <v>28</v>
+      </c>
+      <c r="S23">
+        <f t="shared" ref="S23:S25" si="14">AVERAGE(M23,N23)</f>
+        <v>13.5</v>
+      </c>
+      <c r="T23">
+        <f t="shared" ref="T23:T25" si="15">AVERAGE(Q23:S23)</f>
+        <v>26</v>
+      </c>
+      <c r="U23">
+        <f t="shared" ref="U23:U25" si="16">MIN(Q23:S23)</f>
+        <v>13.5</v>
+      </c>
+      <c r="V23">
+        <f t="shared" ref="V23:V25" si="17">(T23-U23)</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>61</v>
+      </c>
+      <c r="C24">
+        <v>39</v>
+      </c>
+      <c r="D24">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>77</v>
+      </c>
+      <c r="G24">
+        <v>64</v>
+      </c>
+      <c r="H24">
+        <v>36</v>
+      </c>
+      <c r="I24">
+        <v>31</v>
+      </c>
+      <c r="J24">
+        <v>69</v>
+      </c>
+      <c r="L24">
+        <v>91</v>
+      </c>
+      <c r="M24">
+        <v>9</v>
+      </c>
+      <c r="N24">
+        <v>12</v>
+      </c>
+      <c r="O24">
+        <v>88</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="12"/>
+        <v>31</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="13"/>
+        <v>33.5</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="14"/>
+        <v>10.5</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="15"/>
+        <v>25</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="16"/>
+        <v>10.5</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="17"/>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>73</v>
+      </c>
+      <c r="C25">
+        <v>27</v>
+      </c>
+      <c r="D25">
+        <v>37</v>
+      </c>
+      <c r="E25">
+        <v>63</v>
+      </c>
+      <c r="G25">
+        <v>77</v>
+      </c>
+      <c r="H25">
+        <v>23</v>
+      </c>
+      <c r="I25">
+        <v>48</v>
+      </c>
+      <c r="J25">
+        <v>52</v>
+      </c>
+      <c r="L25">
+        <v>93</v>
+      </c>
+      <c r="M25">
+        <v>7</v>
+      </c>
+      <c r="N25">
+        <v>19</v>
+      </c>
+      <c r="O25">
+        <v>81</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="12"/>
+        <v>32</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="13"/>
+        <v>35.5</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="14"/>
+        <v>13</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="15"/>
+        <v>26.833333333333332</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="17"/>
+        <v>13.833333333333332</v>
+      </c>
+    </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
@@ -10245,53 +10868,53 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q68" t="e">
-        <f t="shared" ref="Q68:Q109" si="12">AVERAGE(C68,D68)</f>
+        <f t="shared" ref="Q68:Q109" si="18">AVERAGE(C68,D68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="R68" t="e">
-        <f t="shared" ref="R68:R109" si="13">AVERAGE(H68:I68)</f>
+        <f t="shared" ref="R68:R109" si="19">AVERAGE(H68:I68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S68" t="e">
-        <f t="shared" ref="S68:S109" si="14">AVERAGE(M68,N68)</f>
+        <f t="shared" ref="S68:S109" si="20">AVERAGE(M68,N68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T68" t="e">
-        <f t="shared" ref="T68:T109" si="15">AVERAGE(Q68:S68)</f>
+        <f t="shared" ref="T68:T109" si="21">AVERAGE(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U68" t="e">
-        <f t="shared" ref="U68:U109" si="16">MIN(Q68:S68)</f>
+        <f t="shared" ref="U68:U109" si="22">MIN(Q68:S68)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" t="e">
-        <f t="shared" ref="V68:V109" si="17">(1/3)*(T68-U68)</f>
+        <f t="shared" ref="V68:V109" si="23">(1/3)*(T68-U68)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q69" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R69" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S69" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T69" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U69" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V69" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10307,27 +10930,27 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q73" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R73" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S73" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T73" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U73" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V73" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC73" t="e">
@@ -10349,53 +10972,53 @@
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q74" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R74" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S74" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T74" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U74" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V74" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q75" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R75" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S75" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T75" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U75" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V75" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10411,27 +11034,27 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q79" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R79" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S79" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T79" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U79" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V79" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC79" t="e">
@@ -10453,235 +11076,235 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q80" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R80" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S80" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T80" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U80" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V80" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q81" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R81" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S81" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T81" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U81" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V81" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q82" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R82" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S82" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T82" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U82" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V82" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q83" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R83" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S83" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T83" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U83" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V83" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q84" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R84" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S84" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T84" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U84" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V84" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q85" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R85" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S85" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T85" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U85" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V85" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q86" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R86" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S86" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T86" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U86" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V86" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q87" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R87" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S87" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T87" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U87" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V87" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q88" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R88" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S88" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T88" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U88" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V88" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10697,27 +11320,27 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q92" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R92" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S92" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T92" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U92" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V92" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC92" t="e">
@@ -10739,131 +11362,131 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q93" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R93" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S93" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T93" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U93" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V93" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q94" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R94" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S94" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T94" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U94" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V94" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q95" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R95" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S95" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T95" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U95" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V95" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q96" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R96" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S96" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T96" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U96" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V96" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q97" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R97" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S97" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T97" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U97" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V97" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -10879,27 +11502,27 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q101" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R101" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S101" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T101" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U101" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V101" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AC101" t="e">
@@ -10921,209 +11544,209 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q102" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R102" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S102" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T102" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U102" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V102" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q103" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R103" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S103" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T103" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U103" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V103" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q104" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R104" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S104" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T104" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U104" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V104" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q105" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R105" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S105" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T105" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U105" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V105" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q106" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R106" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S106" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T106" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U106" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V106" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q107" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R107" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S107" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T107" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U107" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V107" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q108" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R108" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S108" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T108" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U108" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.3">
       <c r="Q109" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R109" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S109" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T109" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U109" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -11134,7 +11757,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="23" max="23" width="13.109375" customWidth="1"/>
@@ -11425,6 +12048,232 @@
       <c r="V5">
         <f t="shared" si="5"/>
         <v>14.833333333333332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>64</v>
+      </c>
+      <c r="C9">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>72</v>
+      </c>
+      <c r="H9">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>34</v>
+      </c>
+      <c r="J9">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>92</v>
+      </c>
+      <c r="M9">
+        <v>8</v>
+      </c>
+      <c r="N9">
+        <v>9</v>
+      </c>
+      <c r="O9">
+        <v>91</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q6:Q11" si="6">AVERAGE(C9:D9)</f>
+        <v>28</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R6:R11" si="7">AVERAGE(H9:I9)</f>
+        <v>31</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S6:S11" si="8">AVERAGE(M9:N9)</f>
+        <v>8.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T6:T11" si="9">AVERAGE(Q9:S9)</f>
+        <v>22.5</v>
+      </c>
+      <c r="U9">
+        <f t="shared" ref="U6:U11" si="10">MIN(Q9:S9)</f>
+        <v>8.5</v>
+      </c>
+      <c r="V9">
+        <f t="shared" ref="V6:V11" si="11">T9-U9</f>
+        <v>14</v>
+      </c>
+      <c r="W9">
+        <f>AVERAGE(Q9:Q11)</f>
+        <v>30.666666666666668</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.STDEV.S(Q9:Q11)</f>
+        <v>5.0579969684978323</v>
+      </c>
+      <c r="Y9">
+        <f>AVERAGE(R9:R11)</f>
+        <v>30.666666666666668</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.STDEV.S(R9:R11)</f>
+        <v>4.5092497528228863</v>
+      </c>
+      <c r="AA9">
+        <f>AVERAGE(S9:S11)</f>
+        <v>10.833333333333334</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.STDEV.S(S9:S11)</f>
+        <v>2.8431203515386652</v>
+      </c>
+      <c r="AC9">
+        <f>AVERAGE(T9:T11)</f>
+        <v>24.055555555555557</v>
+      </c>
+      <c r="AD9">
+        <f>_xlfn.STDEV.S(T9:T11)</f>
+        <v>2.6943012562182544</v>
+      </c>
+      <c r="AE9">
+        <f>AVERAGE(V9:V11)</f>
+        <v>13.222222222222223</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.STDEV.S(V9:V11)</f>
+        <v>4.3853713048590777</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>71</v>
+      </c>
+      <c r="C10">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+      <c r="E10">
+        <v>74</v>
+      </c>
+      <c r="G10">
+        <v>72</v>
+      </c>
+      <c r="H10">
+        <v>28</v>
+      </c>
+      <c r="I10">
+        <v>24</v>
+      </c>
+      <c r="J10">
+        <v>76</v>
+      </c>
+      <c r="L10">
+        <v>89</v>
+      </c>
+      <c r="M10">
+        <v>11</v>
+      </c>
+      <c r="N10">
+        <v>17</v>
+      </c>
+      <c r="O10">
+        <v>83</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>27.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="8"/>
+        <v>14</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>22.5</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="10"/>
+        <v>14</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="11"/>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>53</v>
+      </c>
+      <c r="C11">
+        <v>47</v>
+      </c>
+      <c r="D11">
+        <v>26</v>
+      </c>
+      <c r="E11">
+        <v>74</v>
+      </c>
+      <c r="G11">
+        <v>51</v>
+      </c>
+      <c r="H11">
+        <v>49</v>
+      </c>
+      <c r="I11">
+        <v>21</v>
+      </c>
+      <c r="J11">
+        <v>79</v>
+      </c>
+      <c r="L11">
+        <v>91</v>
+      </c>
+      <c r="M11">
+        <v>9</v>
+      </c>
+      <c r="N11">
+        <v>11</v>
+      </c>
+      <c r="O11">
+        <v>89</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>36.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>35</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>27.166666666666668</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="11"/>
+        <v>17.166666666666668</v>
       </c>
     </row>
   </sheetData>
@@ -14878,7 +15727,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
-  <dimension ref="A2:AF9"/>
+  <dimension ref="A2:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -15360,6 +16209,232 @@
         <v>11.833333333333332</v>
       </c>
     </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>69</v>
+      </c>
+      <c r="C12">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12">
+        <v>89</v>
+      </c>
+      <c r="G12">
+        <v>80</v>
+      </c>
+      <c r="H12">
+        <v>20</v>
+      </c>
+      <c r="I12">
+        <v>22</v>
+      </c>
+      <c r="J12">
+        <v>78</v>
+      </c>
+      <c r="L12">
+        <v>89</v>
+      </c>
+      <c r="M12">
+        <v>11</v>
+      </c>
+      <c r="N12">
+        <v>16</v>
+      </c>
+      <c r="O12">
+        <v>84</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" ref="Q10:Q14" si="6">AVERAGE(C12,D12)</f>
+        <v>21</v>
+      </c>
+      <c r="R12">
+        <f t="shared" ref="R10:R14" si="7">AVERAGE(H12,I12)</f>
+        <v>21</v>
+      </c>
+      <c r="S12">
+        <f t="shared" ref="S10:S14" si="8">AVERAGE(M12,N12)</f>
+        <v>13.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T10:T14" si="9">AVERAGE(Q12:S12)</f>
+        <v>18.5</v>
+      </c>
+      <c r="U12">
+        <f>AVERAGE(Q12:Q17)</f>
+        <v>22.333333333333332</v>
+      </c>
+      <c r="V12">
+        <f>_xlfn.STDEV.S(Q12:Q17)</f>
+        <v>3.2145502536643242</v>
+      </c>
+      <c r="W12">
+        <f>AVERAGE(R12:R17)</f>
+        <v>21</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.STDEV.S(R12:R17)</f>
+        <v>4</v>
+      </c>
+      <c r="Y12">
+        <f>AVERAGE(S12:S18)</f>
+        <v>10.333333333333334</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.STDEV.S(S12:S17)</f>
+        <v>3.2532035493238571</v>
+      </c>
+      <c r="AA12">
+        <f>AVERAGE(T12:T17)</f>
+        <v>17.888888888888889</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.STDEV.S(T12:T17)</f>
+        <v>1.0584754935143132</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" ref="AC10:AC14" si="10">MIN(Q12:S12)</f>
+        <v>13.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" ref="AD10:AD14" si="11">T12-AC12</f>
+        <v>5</v>
+      </c>
+      <c r="AE12">
+        <f>AVERAGE(AD12:AD17)</f>
+        <v>7.5555555555555562</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.STDEV.S(AD12:AD17)</f>
+        <v>2.364866294865863</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>75</v>
+      </c>
+      <c r="C13">
+        <v>25</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>85</v>
+      </c>
+      <c r="G13">
+        <v>86</v>
+      </c>
+      <c r="H13">
+        <v>14</v>
+      </c>
+      <c r="I13">
+        <v>36</v>
+      </c>
+      <c r="J13">
+        <v>64</v>
+      </c>
+      <c r="L13">
+        <v>92</v>
+      </c>
+      <c r="M13">
+        <v>8</v>
+      </c>
+      <c r="N13">
+        <v>13</v>
+      </c>
+      <c r="O13">
+        <v>87</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>10.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>18.5</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>10.5</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>62</v>
+      </c>
+      <c r="C14">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>86</v>
+      </c>
+      <c r="G14">
+        <v>84</v>
+      </c>
+      <c r="H14">
+        <v>16</v>
+      </c>
+      <c r="I14">
+        <v>18</v>
+      </c>
+      <c r="J14">
+        <v>82</v>
+      </c>
+      <c r="L14">
+        <v>94</v>
+      </c>
+      <c r="M14">
+        <v>6</v>
+      </c>
+      <c r="N14">
+        <v>8</v>
+      </c>
+      <c r="O14">
+        <v>92</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="9"/>
+        <v>16.666666666666668</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>9.6666666666666679</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
